--- a/ig/DM-37/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="1133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="1283">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -172,6 +172,9 @@
     <t>Addictologie comportementale (sans substance)</t>
   </si>
   <si>
+    <t>Branche de la médecine qui étudie la difficulté ou l'impossibilité de contrôler un comportement malgré ses conséquences. Elle comprend les addictions aux jeux d'argent, aux jeux vidéo, aux écrans, à Internet, à la nourriture et au sexe.</t>
+  </si>
+  <si>
     <t>002</t>
   </si>
   <si>
@@ -184,6 +187,9 @@
     <t>Alcoologie</t>
   </si>
   <si>
+    <t>Branche de la médecine qui étudie les causes et les effets de la consommation d'alcool par l'être humain.</t>
+  </si>
+  <si>
     <t>004</t>
   </si>
   <si>
@@ -358,12 +364,18 @@
     <t>Chirurgie vasculaire et endovasculaire</t>
   </si>
   <si>
+    <t>Spécialité chirurgicale qui s'applique aux vaisseaux (artères ou veines) prenant en charge les maladies artérielles : dilatations pathologiques graves (anévrismes de l'aorte), rétrécissements artériels par artériosclérose (par exemple, pontage au niveau de la cuisse pour artérite de jambes), maladies veineuses (varices) et la mise en place de dispositifs reliés à de gros vaisseaux (par exemple, les chambres implantables).</t>
+  </si>
+  <si>
     <t>033</t>
   </si>
   <si>
     <t>Chirurgie digestive et viscérale fonctionnelle (hors carcinologie)</t>
   </si>
   <si>
+    <t>Branche de la chirurgie dont le périmètre d'intervention est l'ensemble des organes digestifs et endocriniens, de l'oesophage jusqu'à l'anus en y excluant les pathologies cancéreuses.</t>
+  </si>
+  <si>
     <t>034</t>
   </si>
   <si>
@@ -406,6 +418,9 @@
     <t>Diététique et Nutrition</t>
   </si>
   <si>
+    <t>La diététique désigne l'ensemble des règles à suivre pour une alimentation bien équilibrée. La nutrition est axée sur l'assimilation et la transformation par le corps des nutriments.</t>
+  </si>
+  <si>
     <t>041</t>
   </si>
   <si>
@@ -430,6 +445,9 @@
     <t>Foetopathologie et Embryopathologie</t>
   </si>
   <si>
+    <t>Spécialité médicale réalisant l'examen médical approfondi des embryons et des foetus, qu'ils soient issus d'une interruption spontanée de grossesse, ou d'une interruption médicale de grossesse. Il s'y ajoute habituellement l'examen des nouveau-nés décédés en période néonatale.</t>
+  </si>
+  <si>
     <t>045</t>
   </si>
   <si>
@@ -628,6 +646,9 @@
     <t>Maladies infectieuses et tropicales</t>
   </si>
   <si>
+    <t>Spécialité médicale clinique qui s'intéresse à la prise en charge des maladies infectieuses et tropicales (c'est-à-dire transmis par les bactéries, virus, parasites ou champignons) dans leurs dimensions individuelles et collectives.</t>
+  </si>
+  <si>
     <t>078</t>
   </si>
   <si>
@@ -670,12 +691,18 @@
     <t>Médecine hyperbare</t>
   </si>
   <si>
+    <t>Branche de la médecine qui utilise l'oxygénothérapie hyperbare, qui est une méthode d'administration d'oxygène (O2) inhalé à des fins thérapeutiques sous une pression supérieure à la pression atmosphérique. Elle est appliquée par l'intermédiaire d'une chambre hyperbare, communément appelée « caisson ».</t>
+  </si>
+  <si>
     <t>085</t>
   </si>
   <si>
     <t>Médecine interne</t>
   </si>
   <si>
+    <t>Spécialité médicale qui s'intéresse au diagnostic et à la prise en charge globale des maladies de l'adulte, et particulièrement des maladies systémiques et auto-immunes en général.</t>
+  </si>
+  <si>
     <t>086</t>
   </si>
   <si>
@@ -760,6 +787,9 @@
     <t>Médecine de l'obésité</t>
   </si>
   <si>
+    <t>Branche de la médecine qui prend en charge les patients atteints d'obésité.</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
@@ -772,12 +802,18 @@
     <t>Odontologie (dentaire)</t>
   </si>
   <si>
+    <t>Spécialité médico-chirurgicale qui traite de la prévention, du diagnostic et du traitement des maladies congénitales ou acquises, réelles ou supposées, de la bouche, des dents, des maxillaires et des tissus connexes.</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
     <t>Oncologie médicale (cancérologie)</t>
   </si>
   <si>
+    <t>Spécialité médicale qui s'intéresse aux tumeurs cancéreuses. On parle aussi de cancérologie.</t>
+  </si>
+  <si>
     <t>103</t>
   </si>
   <si>
@@ -790,18 +826,27 @@
     <t>Orthodontie ou orthopédie dento-faciale</t>
   </si>
   <si>
+    <t>Spécialité qui traite les anomalies des arcades dentaires, les anomalies de position des dents, les anomalies des mâchoires et les dysfonctions associées.</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
     <t>Orthogénie</t>
   </si>
   <si>
+    <t>Branche de la médecine qui s'occupe des différents moyens de contraception et des méthodes d'interruption volontaire de grossesse.</t>
+  </si>
+  <si>
     <t>106</t>
   </si>
   <si>
     <t>Orthoptie</t>
   </si>
   <si>
+    <t>Discipline paramédicale spécialisée dans le dépistage, la rééducation et l'exploration de la fonction visuelle.</t>
+  </si>
+  <si>
     <t>107</t>
   </si>
   <si>
@@ -868,6 +913,9 @@
     <t>Proctologie médico-chirurgicale</t>
   </si>
   <si>
+    <t>Branche de la médecine et de la chirurgie qui s'intéresse aux maladies de l'anus et du rectum.</t>
+  </si>
+  <si>
     <t>118</t>
   </si>
   <si>
@@ -958,6 +1006,9 @@
     <t>Rythmologie</t>
   </si>
   <si>
+    <t>Branche de la cardiologie (surspécialité) dédiée à la prise en charge des anomalies du rythme cardiaque, extrasystoles, accélération ou ralentissements anormaux.</t>
+  </si>
+  <si>
     <t>133</t>
   </si>
   <si>
@@ -976,6 +1027,9 @@
     <t>Sexologie médicale</t>
   </si>
   <si>
+    <t>Branche de la médecine qui étudie les troubles de la sexualité.</t>
+  </si>
+  <si>
     <t>136</t>
   </si>
   <si>
@@ -1150,6 +1204,9 @@
     <t>Traitements médicamenteux systémiques du cancer</t>
   </si>
   <si>
+    <t>Regroupent la chimiothérapie, les thérapies ciblées, l'immunothérapie et les médicaments de thérapie innovante, quelles que soient les voies d'administration.</t>
+  </si>
+  <si>
     <t>165</t>
   </si>
   <si>
@@ -1174,6 +1231,9 @@
     <t>Radiothérapie externe</t>
   </si>
   <si>
+    <t>Traitement du cancer dont le but est de détruire les cellules cancéreuses à travers la peau au moyen de rayons produits par un appareil de radiothérapie, un accélérateur de particules dont les rayons sont dirigés en faisceau sur la tumeur et parfois, sur certains ganglions voisins de l'organe atteint.</t>
+  </si>
+  <si>
     <t>169</t>
   </si>
   <si>
@@ -1186,6 +1246,9 @@
     <t>Soins palliatifs</t>
   </si>
   <si>
+    <t>Ensemble des actes de soin et d'accompagnement à visée palliative (visent au confort du malade) réalisés par des professionnels formés qui exercent dans une structure médico-sociale et peuvent intervenir sur tous les lieux de vie de l'usager.</t>
+  </si>
+  <si>
     <t>171</t>
   </si>
   <si>
@@ -1198,6 +1261,9 @@
     <t>Réadaptation polyvalente</t>
   </si>
   <si>
+    <t>Branche des soins médicaux et de réadaptation qui vise à prévenir ou à réduire les conséquences fonctionnelles, les déficiences et les limitations d'activité, soit dans le cadre de la prise en charge de patients atteints de pathologies chroniques, soit en amont ou en aval des épisodes de soins aigus, que ces conséquences soient physiques, cognitives, psychologiques ou sociales.</t>
+  </si>
+  <si>
     <t>173</t>
   </si>
   <si>
@@ -1231,12 +1297,18 @@
     <t>Chirurgie plastique et esthétique</t>
   </si>
   <si>
+    <t>Spécialité chirurgicale qui reconstruit et améliore l'apparence du corps à la suite d'une malformation congénitale, d'un accident, d'une intervention chirurgicale, d'une anomalie morphologique ou encore l'aspect extérieur du corps mal accepté par le patient.</t>
+  </si>
+  <si>
     <t>179</t>
   </si>
   <si>
     <t>Médecine aéronautique et aérospatiale</t>
   </si>
   <si>
+    <t>Branche de médecine qui prend en charge les effets physiologiques du vol dans l'atmosphère pour l'évaluation et la surveillance médicale des personnels navigants.</t>
+  </si>
+  <si>
     <t>180</t>
   </si>
   <si>
@@ -1279,48 +1351,72 @@
     <t>Oncologie médicale neurologique (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses du système nerveux central et périphérique.</t>
+  </si>
+  <si>
     <t>187</t>
   </si>
   <si>
     <t>Oncogériatrie médicale (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses du patient âgé pour un traitement adapté à son état grâce à une approche multidisciplinaire et multiprofessionnelle.</t>
+  </si>
+  <si>
     <t>188</t>
   </si>
   <si>
     <t>Oncologie médicale dermatologique (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses de la peau et des muqueuses.</t>
+  </si>
+  <si>
     <t>189</t>
   </si>
   <si>
     <t>Oncologie médicale digestive et viscérale (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses des affections de l'abdomen et du pelvis.</t>
+  </si>
+  <si>
     <t>190</t>
   </si>
   <si>
     <t>Oncologie médicale gynécologique (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses de l'appareil génital de la femme (utérus, vagin, ovaires, et seins).</t>
+  </si>
+  <si>
     <t>191</t>
   </si>
   <si>
     <t>Oncologie médicale hématologique (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'hématologie qui s'intéresse aux cancers des cellules du sang et des organes qui les fabriquent, comme les leucémies ou les lymphomes.</t>
+  </si>
+  <si>
     <t>192</t>
   </si>
   <si>
     <t>Oncologie médicale ORL et cervico-faciale (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses de l'oreille, du nez et de la gorge.</t>
+  </si>
+  <si>
     <t>193</t>
   </si>
   <si>
     <t>Oncologie médicale pneumologique (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses de l'appareil respiratoire.</t>
+  </si>
+  <si>
     <t>194</t>
   </si>
   <si>
@@ -1333,12 +1429,18 @@
     <t>Oncologie médicale sénologique (cancer du sein) (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses du sein.</t>
+  </si>
+  <si>
     <t>196</t>
   </si>
   <si>
     <t>Oncologie médicale urologique (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses de l'appareil urinaire de la femme et de l'homme (vessie, uretère, urètre) et de l'appareil génital et reproducteur masculin (prostate, pénis, testicules).</t>
+  </si>
+  <si>
     <t>197</t>
   </si>
   <si>
@@ -1351,24 +1453,36 @@
     <t>Parodontologie</t>
   </si>
   <si>
+    <t>Discipline de prévention et traitement des affections des gencives et de l'os qui entoure les dents.</t>
+  </si>
+  <si>
     <t>199</t>
   </si>
   <si>
     <t>Chirurgie orale</t>
   </si>
   <si>
+    <t>Spécialité qui traite les pathologies des mâchoires et des tissus environnants.</t>
+  </si>
+  <si>
     <t>200</t>
   </si>
   <si>
     <t>Orthophonie</t>
   </si>
   <si>
+    <t>Discipline paramédicale spécialisée dans la prévention, le bilan orthophonique et le traitement des troubles de la communication, du langage dans toutes ses dimensions, de la cognition mathématique, de la parole, de la voix et des fonctions oro-myo-faciales</t>
+  </si>
+  <si>
     <t>201</t>
   </si>
   <si>
     <t>Podologie</t>
   </si>
   <si>
+    <t>Discipline paramédicale qualifiée pour traiter directement les affections épidermiques, limitées aux couches cornées et aux affections unguéales du pied, à l'exclusion de toute intervention chirurgicale, pour pratiquer les soins d'hygiène, pour confectionner et appliquer des semelles destinées à prévenir ou à soulager les affections épidermiques, pour analyser et évaluer les troubles morphostatiques et dynamiques du pied et élaborer un diagnostic de pédicurie-podologie en tenant compte de la statique et de la dynamique du pied, pour renouveler les prescriptions médicales initiales d'orthèses plantaires.</t>
+  </si>
+  <si>
     <t>202</t>
   </si>
   <si>
@@ -1519,6 +1633,9 @@
     <t>Expertise des infections osteo-articulaires complexes (CRIOA, CRIOAC)</t>
   </si>
   <si>
+    <t>Centres de référence qui ont une mission de coordination, d'expertise, de formation et de recherche ainsi que de prise en charge des infections ostéo-articulaires les plus complexes en lien avec leurs centres correspondants et les autres établissements de l'inter-région.</t>
+  </si>
+  <si>
     <t>227</t>
   </si>
   <si>
@@ -1549,6 +1666,9 @@
     <t>Evaluation et soins de réhabilitation psychosociale</t>
   </si>
   <si>
+    <t>Evaluation et soins mis en oeuvre auprès des personnes souffrant de troubles psychiques visant à favoriser leur autonomie et leur intégration pour atteindre une qualité de vie satisfaisante en tenant compte de leurs capacités, leurs compétences et leurs choix</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
@@ -1561,12 +1681,18 @@
     <t>Réadaptation des affections de l'appareil locomoteur</t>
   </si>
   <si>
+    <t>Prise en charge des affections de l'appareil locomoteur permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections de l'appareil locomoteur sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
     <t>Réadaptation des affections du système nerveux</t>
   </si>
   <si>
+    <t>Ensemble d'interventions conçues pour optimiser le fonctionnement et réduire le handicap des personnes souffrant de problèmes de santé lorsqu'elles interagissent avec leur environnement.</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
@@ -1597,6 +1723,9 @@
     <t>Réadaptation des brulés (dont maladies nécrosantes et bulleuses de la peau)</t>
   </si>
   <si>
+    <t>Branche des soins médicaux et de réadaptation qui vise à prévenir ou à réduire les conséquences fonctionnelles, les déficiences et les limitations d'activité conçues pour optimiser le fonctionnement et réduire le handicap des personnes souffrant de brûlures ou de lésions cutanées nécrosantes ou bulleuses.</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
@@ -1609,6 +1738,9 @@
     <t>Réadaptation gériatrique</t>
   </si>
   <si>
+    <t>Prise en charge des affections gériatriques permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections dues à l'âge sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
     <t>242</t>
   </si>
   <si>
@@ -1621,6 +1753,9 @@
     <t>Réadaptation néphrologie</t>
   </si>
   <si>
+    <t>Prise en charge des affections de l'appareil rénal permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections néphrologiques sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
     <t>244</t>
   </si>
   <si>
@@ -1837,6 +1972,9 @@
     <t>Oncologie médicale pédiatrique (cancérologie)</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses de l'enfant et de l'adolescent.</t>
+  </si>
+  <si>
     <t>280</t>
   </si>
   <si>
@@ -1849,12 +1987,18 @@
     <t>Chirurgie oncologique</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>282</t>
   </si>
   <si>
     <t>Périnatalité (suivi de grossesse)</t>
   </si>
   <si>
+    <t>Prise en charge du suivi de grossesse et du post accouchement du nouveau-né et de la maman.</t>
+  </si>
+  <si>
     <t>283</t>
   </si>
   <si>
@@ -1882,6 +2026,9 @@
     <t>Soins infirmiers</t>
   </si>
   <si>
+    <t>Ensemble des actes de soin et d'accompagnement à visée préventive, curative, palliative réalisés par un(e) infirmier(e) diplômée d'état (IDE) qui exerce dans une structure médico-sociale et peut intervenir sur tous les lieux de vie de l'usager.</t>
+  </si>
+  <si>
     <t>288</t>
   </si>
   <si>
@@ -1900,18 +2047,27 @@
     <t>Réadaptation des fonctions du langage et de la communication</t>
   </si>
   <si>
+    <t>Ensemble des actes réalisés par des professionnels formés qui visent à rétablir ou maintenir les fonctions de la parole ou à élaborer des stratégies de contournement permettant à la personne de communiquer en tenant compte de ses caractéristiques individuelles.</t>
+  </si>
+  <si>
     <t>291</t>
   </si>
   <si>
     <t>Réadaptation pour la mobilité</t>
   </si>
   <si>
+    <t>Ensemble des actes réalisés par des professionnels formés qui visent à rétablir ou maintenir les fonctions de locomotion ou à élaborer des stratégies de contournement permettant à la personne de se déplacer en tenant compte de ses caractéristiques individuelles.</t>
+  </si>
+  <si>
     <t>292</t>
   </si>
   <si>
     <t>Réadaptation des fonctions cognitives</t>
   </si>
   <si>
+    <t>Ensemble des actes réalisés par des professionnels formés qui visent à rétablir ou maintenir les fonctions cognitives (fonctions de percevoir, de prêter attention, de mémoriser, de raisonner, de produire des mouvements, de s'exprimer).</t>
+  </si>
+  <si>
     <t>293</t>
   </si>
   <si>
@@ -1972,6 +2128,9 @@
     <t>Accompagnements pour préparer sa vie professionnelle</t>
   </si>
   <si>
+    <t>Ensemble des actes d'accompagnement visant à l'élaboration d'un projet professionnel. Ces actes comprennent un temps de bilan et d'accompagnement, notamment par l'intermédiaire des dispositifs de droit commun, pour l'orientation professionnelle ou la réorientation professionnelle (dont la recherche de stage et la recherche d'un emploi).</t>
+  </si>
+  <si>
     <t>303</t>
   </si>
   <si>
@@ -2032,12 +2191,18 @@
     <t>Accompagnements pour créer ou maintenir le lien social et éviter l'isolement</t>
   </si>
   <si>
+    <t>Ensemble des actes d'accompagnement visant à permettre à la personne de créer et maintenir le lien avec d'autres personnes. En établissement médico-social, il peut notamment s'agir de l'accompagnement dans la mise en relation, de la médiation des premiers échanges et du soutien aux relations amicales dans l'établissement.</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
     <t>Accompagnements à des activités sociales, culturelles, sportives et de loisirs</t>
   </si>
   <si>
+    <t>Ensemble des actes d'accompagnement éducatif réalisés en dehors de la structure médico-sociale pour la mise en oeuvre d'activités sportives, culturelles, de loisirs.</t>
+  </si>
+  <si>
     <t>314</t>
   </si>
   <si>
@@ -2110,6 +2275,9 @@
     <t>Soutien et aide aux aidants et/ou à la famille/entourage</t>
   </si>
   <si>
+    <t>Soutien et aide aux aidants et/ou à la famille concernant les besoins de la personne accompagnée, pouvant être liés aux actes du quotidien, à la communication, aux relations avec autrui ainsi qu'aux gestes assurant sa santé.</t>
+  </si>
+  <si>
     <t>326</t>
   </si>
   <si>
@@ -2164,12 +2332,18 @@
     <t>Activité de prévention</t>
   </si>
   <si>
+    <t>Ensemble des activités et techniques visant à éviter ou réduire le nombre et la gravité des maladies, des accidents et des handicaps.</t>
+  </si>
+  <si>
     <t>335</t>
   </si>
   <si>
     <t>Coordination de parcours complexes</t>
   </si>
   <si>
+    <t>Organisation et coordination des interventions des différents acteurs identifiés lorsqu'un risque de rupture de parcours est identifié ou que la rupture est avérée. Une accumulation de paramètres vient dessiner cette situation complexe : sur le plan social, économique, environnemental, culturel…</t>
+  </si>
+  <si>
     <t>336</t>
   </si>
   <si>
@@ -2188,18 +2362,27 @@
     <t>Neuroradiologie</t>
   </si>
   <si>
+    <t>Branche de la radiologie spécialisée dans les pathologies du système nerveux, la neuroradiologie comporte l'« imagerie diagnostique » (radiographie, scanner, IRM, échographie et artériographie), et l'« imagerie interventionnelle » avec l'activité de neuroradiologie interventionnelle (NRI) à visée thérapeutique (infiltration rachidienne sous scanner, traitement des malformations vasculaires cérébrales) et la prise en charge des AVC (accident vasculaire cérébral).</t>
+  </si>
+  <si>
     <t>339</t>
   </si>
   <si>
     <t>Kinésithérapie</t>
   </si>
   <si>
+    <t>Discipline paramédicale dont la pratique comprend la promotion de la santé, la prévention, la kinésithérapie le diagnostic et le traitement : du mouvement ou des troubles moteurs de la personne et des déficiences ou altérations des capacités fonctionnelles.</t>
+  </si>
+  <si>
     <t>340</t>
   </si>
   <si>
     <t>Coordination plan de soins</t>
   </si>
   <si>
+    <t>Ensemble des actes visant une coordination renforcée pour la cohérence du parcours de soins.</t>
+  </si>
+  <si>
     <t>341</t>
   </si>
   <si>
@@ -2242,6 +2425,9 @@
     <t>Exploration fonctionnelle ORL</t>
   </si>
   <si>
+    <t>Examen(s) destiné(s) à apprécier la manière dont un organe assure sa fonction.</t>
+  </si>
+  <si>
     <t>348</t>
   </si>
   <si>
@@ -2362,6 +2548,9 @@
     <t>Soins intensifs spécialisés hépato-gastro-entérologie (USIG)</t>
   </si>
   <si>
+    <t>Unités d'un établissement de santé organisées pour prendre en charge des patients qui présentent ou sont susceptibles de présenter une défaillance aiguë de l'organe concerné par la spécialité médicale en hépato-gastro-entérologie mettant directement en jeu à court terme leur pronostic vital et impliquant le recours à une méthode de suppléance.</t>
+  </si>
+  <si>
     <t>368</t>
   </si>
   <si>
@@ -2542,6 +2731,9 @@
     <t>Pharmacie à Usage Intérieur (PUI)</t>
   </si>
   <si>
+    <t>Pharmacie installée au sein d'un groupement hospitalier de territoire ou d'un groupement de coopération sanitaire dans lequel elles ont été constituées établissement de santé, établissements médico-sociaux pour répondre aux besoins pharmaceutiques des personnes prises en charge par ces établissements ou structures.</t>
+  </si>
+  <si>
     <t>398</t>
   </si>
   <si>
@@ -2584,6 +2776,9 @@
     <t>Addictologie avec substance(s)</t>
   </si>
   <si>
+    <t>Dépendance qui se caractérise par un désir souvent puissant, voire compulsif, de consommer une substance.</t>
+  </si>
+  <si>
     <t>405</t>
   </si>
   <si>
@@ -2614,12 +2809,18 @@
     <t>Oncologie médicale endocrinienne et thyroïdienne</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses des glandes sécrétrices d'hormones : hypophyse, thyroïde, glandes surrénales…</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
     <t>Oncologie médicale os et tissus mous</t>
   </si>
   <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses des tissus mous, sarcome (muscle, graisse, nerf, vaisseaux sanguins…), et des cancers primitifs de l'os.</t>
+  </si>
+  <si>
     <t>411</t>
   </si>
   <si>
@@ -2764,12 +2965,18 @@
     <t>Elaboration du plan d'aide individualisé</t>
   </si>
   <si>
+    <t>résultat de l'action d'expertise menée par des équipes, en général mobiles, qui étudient une situation et déterminent les actions à mettre en oeuvre pour le bénéficiaire, mais ne mènent pas la coordination de la réalisation du plan d'aide.</t>
+  </si>
+  <si>
     <t>435</t>
   </si>
   <si>
     <t>Expertise médicale (évaluation de préjudice)</t>
   </si>
   <si>
+    <t>L'expertise médicale est un moyen d'investigation qui éclaire une juridiction ou des parties, sur des questions strictement techniques, et dont la connaissance ou l'explication est nécessaire pour rapporter la vérité ou solutionner un litige. L'expertise médicale a pour but, dans le cadre du dommage corporel ou dans celui des accidents du travail, d'évaluer les séquelles fonctionnelles des victimes d'accidents.</t>
+  </si>
+  <si>
     <t>436</t>
   </si>
   <si>
@@ -2782,6 +2989,9 @@
     <t>Médecine générale</t>
   </si>
   <si>
+    <t>La médecine générale (MG) est la branche de la médecine prenant en charge la prévention, les soins médicaux et le traitement des malades, sans se limiter à des groupes de maladies relevant d'un organe, d'un âge, ou d'un sexe particulier.</t>
+  </si>
+  <si>
     <t>438</t>
   </si>
   <si>
@@ -2794,84 +3004,126 @@
     <t>Gynécologie endocrinienne</t>
   </si>
   <si>
+    <t>L'endocrinologie gynécologique comprend la détection et le traitement des maladies hormonales des différentes phases de la vie génitale de la femme.</t>
+  </si>
+  <si>
     <t>440</t>
   </si>
   <si>
     <t>Chirurgie intracrânienne</t>
   </si>
   <si>
+    <t>Chirurgie qui comprend l'ouverture du crane pour y réaliser un geste.</t>
+  </si>
+  <si>
     <t>441</t>
   </si>
   <si>
     <t>Médecine bucco-dentaire</t>
   </si>
   <si>
+    <t>Spécialité qui traite les pathologies lourdes ou spécifiques (handicaps, maladies rares…) des mâchoires et des dents.</t>
+  </si>
+  <si>
     <t>442</t>
   </si>
   <si>
     <t>Chirurgie dentaire</t>
   </si>
   <si>
+    <t>Discipline qui étudie et traite les affections des dents, des tissus attenants et des mâchoires.</t>
+  </si>
+  <si>
     <t>443</t>
   </si>
   <si>
     <t>Pédodontie ou odontologie pédiatrique</t>
   </si>
   <si>
+    <t>Discipline qui étudie et traite les affections des dents, des tissus attenants et des mâchoires chez les enfants et adolescents.</t>
+  </si>
+  <si>
     <t>444</t>
   </si>
   <si>
     <t>Endodontie</t>
   </si>
   <si>
+    <t>Discipline de traitement et prévention des atteintes de la pulpe dentaire et des infections périapicales (ou des racines des dents).</t>
+  </si>
+  <si>
     <t>445</t>
   </si>
   <si>
     <t>Biologie moléculaire sur prélèvement Anapath</t>
   </si>
   <si>
+    <t>Analyse par des médecins anatomo-pathologistes des prélèvements, par biologie moléculaire avec des techniques ciblées (PCR, RT-PCR, hybridation in situ) ou plus larges (NGS) pour recherche de clonalité, de perte d'hétérozygotie, de mutations, de réarrangements, d'amplifications, à visée diagnostique, pronostique ou théranostique de certaines pathologies tumorales</t>
+  </si>
+  <si>
     <t>446</t>
   </si>
   <si>
     <t>Cytopathologie</t>
   </si>
   <si>
+    <t>Etude morphologique des cellules isolées, à partir de produits de ponction, brossage, frottis, aspiration, lavage</t>
+  </si>
+  <si>
     <t>447</t>
   </si>
   <si>
     <t>Histopathologie</t>
   </si>
   <si>
+    <t>Etude morphologique des tissus issus d'examen de prélevés par biopsie, ponction-biopsie, résection endoscopique et résection chirurgicale, avec pour objectif d'identifier les lésions provoquées par les maladies ou associées à celles-ci</t>
+  </si>
+  <si>
     <t>448</t>
   </si>
   <si>
     <t>Diagnostic lié à un retard ou trouble du développement</t>
   </si>
   <si>
+    <t>Diagnostic pour répondre à des besoins relatifs au confort physique, la santé, le bien-être physique et mental.</t>
+  </si>
+  <si>
     <t>449</t>
   </si>
   <si>
     <t>Appui et coopération auprès des acteurs de l'enseignement</t>
   </si>
   <si>
+    <t>Soutien des acteurs de l'enseignement, spécialisé ou de droit commun, dans la prise en charge de l'élève, par l'apport d'une expertise et de ressources médico-sociales</t>
+  </si>
+  <si>
     <t>450</t>
   </si>
   <si>
     <t>Accompagnement à la réduction des risques en addictologie</t>
   </si>
   <si>
+    <t>Ensemble des pratiques qui visent à réduire les conséquences néfastes de l'addiction, tant au niveau sanitaire, psychologique que social. Cet accompagnement peut être initié par une première évaluation médico-psycho-sociale, et peut par exemple comprendre des ateliers de « pratiques à moindre risque » pour les usagers de drogues</t>
+  </si>
+  <si>
     <t>451</t>
   </si>
   <si>
     <t>Exploration et prise en charge des troubles du sommeil</t>
   </si>
   <si>
+    <t>Cette exploration consiste en des examens qui permettent d'enregistrer et d'analyser le sommeil au plan neurologique, respiratoire et cardiologique, ils comprennent entre autres la polysomnographie (correspond à l'exploration nocturne), des tests de maintien d'éveil et des tests de latence d'endormissement correspondent à l'exploration diurne</t>
+  </si>
+  <si>
     <t>452</t>
   </si>
   <si>
     <t>Exploration des troubles psycho-comportementaux et cognitifs</t>
   </si>
   <si>
+    <t>Cette exploration comprend une évaluation du fonctionnement cognitif globale (approche psychométrique) et spécifique (évaluation anatomoclinique, mnésique, cognitive, et écologique), une évaluation du comportement (échelles) et la restitution par un compte-rendu</t>
+  </si>
+  <si>
     <t>453</t>
   </si>
   <si>
@@ -2884,15 +3136,24 @@
     <t>Radiologie polyvalente générale</t>
   </si>
   <si>
+    <t>Partie de la radiologie réalisant les actes généraux de base de radiologie au sens non hyperspécialisé.</t>
+  </si>
+  <si>
     <t>455</t>
   </si>
   <si>
     <t>Médecine thermale</t>
   </si>
   <si>
+    <t>Ensemble des activités médicales liées à l'utilisation et à l'exploitation des eaux thermales et leurs produits dérivés (gaz, boues), associant la thermalité (chaleur), les techniques de soins et des eaux thermales, à visée thérapeutique</t>
+  </si>
+  <si>
     <t>456</t>
   </si>
   <si>
+    <t>Prise en charge médicale spécialisée des affections de l'appareil locomoteur permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections de l'appareil locomoteur sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
     <t>457</t>
   </si>
   <si>
@@ -2941,78 +3202,117 @@
     <t>Chirurgie des varices</t>
   </si>
   <si>
+    <t>Branche de la chirurgie vasculaire qui consiste à traiter les maladies des veines superficielles des membres inférieurs ou du pelvis</t>
+  </si>
+  <si>
     <t>467</t>
   </si>
   <si>
     <t>Chirurgie orthopédique et traumatologique spécialisée main</t>
   </si>
   <si>
+    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme), spécialisé dans la chirurgie qui prend en charge les lésions de la main.</t>
+  </si>
+  <si>
     <t>468</t>
   </si>
   <si>
     <t>Chirurgie orthopédique et traumatologique spécialisée membres inférieurs</t>
   </si>
   <si>
+    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les lésions du membre inférieurs</t>
+  </si>
+  <si>
     <t>469</t>
   </si>
   <si>
     <t>Chirurgie orthopédique et traumatologique spéc. membres supérieurs (sauf main)</t>
   </si>
   <si>
+    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les lésions du membre supérieur en excluant la main.</t>
+  </si>
+  <si>
     <t>470</t>
   </si>
   <si>
     <t>Chirurgie orthopédique et traumatologique spécialisée tumeur</t>
   </si>
   <si>
+    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les tumeurs malignes ou bénignes des os et des tissus mous du membre supérieur et de l'appareil locomoteur</t>
+  </si>
+  <si>
     <t>471</t>
   </si>
   <si>
     <t>Orientation vers un médecin traitant acceptant de nouveaux patients</t>
   </si>
   <si>
+    <t>Activité de coordination visant à orienter un patient, en fonction de ses besoins, vers un médecin traitant prenant de nouveaux patients, vers des soins « non programmés » (urgence non vitale) ou encore vers un professionnel de santé disponible (infirmier, dentiste etc.)</t>
+  </si>
+  <si>
     <t>472</t>
   </si>
   <si>
     <t>Veille et prévention de la récidive suicidaire</t>
   </si>
   <si>
+    <t>Ce dispositif consiste en un système de recontact et d'alerte en organisant autour de la personne ayant fait une tentative de suicide un réseau de professionnels de santé qui garderont le contact avec elle.</t>
+  </si>
+  <si>
     <t>473</t>
   </si>
   <si>
     <t>Chirurgie onco de la sphère ORL, cervico-faciale et maxillo-faciale</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses de la sphère oto-rhino-laryngée, cervico-faciale et maxillo-faciale.</t>
+  </si>
+  <si>
     <t>474</t>
   </si>
   <si>
     <t>Chirurgie oncologique viscérale et digestive</t>
   </si>
   <si>
+    <t>Branche de la chirurgie dont le périmètre d'intervention est l'ensemble des pathologies néoplasiques des organes digestifs et endocriniens, de l'oesophage jusqu'à l'anus.</t>
+  </si>
+  <si>
     <t>475</t>
   </si>
   <si>
     <t>Coordination de soins non-programmés</t>
   </si>
   <si>
+    <t>Organisation de la collaboration des professionnels de santé afin d'améliorer la prise en charge des patients d'une urgence ressentie par le patient, mais ne relevant pas nécessairement d'une urgence médicale à proprement dit.</t>
+  </si>
+  <si>
     <t>476</t>
   </si>
   <si>
     <t>Exploration fonctionnelle de l'audition</t>
   </si>
   <si>
+    <t>Examen(s) destiné(s) à explorer et mesurer le fonctionnement de l'audition.</t>
+  </si>
+  <si>
     <t>477</t>
   </si>
   <si>
     <t>Exploration fonctionnelle de la voix et de la déglutition</t>
   </si>
   <si>
+    <t>Examen(s) destiné(s) à apprécier la manière dont un organe assure sa fonction de phonation et de déglutition.</t>
+  </si>
+  <si>
     <t>478</t>
   </si>
   <si>
     <t>Exploration fonctionnelle des vertiges (audio vestibulaire)</t>
   </si>
   <si>
+    <t>Examen(s) destiné(s) à explorer et mesurer la fonction vestibulaire (otoneurologie).</t>
+  </si>
+  <si>
     <t>479</t>
   </si>
   <si>
@@ -3025,66 +3325,99 @@
     <t>Médecine du sommeil</t>
   </si>
   <si>
+    <t>(= hypnologie ou somnologie) est la branche de la médecine spécialisée dans le diagnostic et le traitement des troubles de la vigilance (somnolence excessive) et du sommeil (insomnies, parasomnies).</t>
+  </si>
+  <si>
     <t>481</t>
   </si>
   <si>
     <t>Médecine générale à orientation Allergologie</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Allergologie.</t>
+  </si>
+  <si>
     <t>482</t>
   </si>
   <si>
     <t>Médecine générale à orientation Andrologie</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Andrologie.</t>
+  </si>
+  <si>
     <t>483</t>
   </si>
   <si>
     <t>Médecine générale à orientation Diabétologie</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Diabétologie.</t>
+  </si>
+  <si>
     <t>484</t>
   </si>
   <si>
     <t>Médecine générale à orientation Gériatrie, Gérontologie</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Gériatrie, Gérontologie.</t>
+  </si>
+  <si>
     <t>485</t>
   </si>
   <si>
     <t>Médecine générale à orientation Gynécologie médicale</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Gynécologie médicale.</t>
+  </si>
+  <si>
     <t>486</t>
   </si>
   <si>
     <t>Médecine générale orientation Maladies infectieuses, parasitaires et tropicales</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Maladies infectieuses, parasitaires et tropicales.</t>
+  </si>
+  <si>
     <t>487</t>
   </si>
   <si>
     <t>Médecine générale à orientation Médecine pédiatrique</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Médecine pédiatrique.</t>
+  </si>
+  <si>
     <t>488</t>
   </si>
   <si>
     <t>Médecine générale à orientation Médecine vasculaire (Angiologie, Phlébologie)</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Médecine vasculaire (Angiologie, Phlébologie).</t>
+  </si>
+  <si>
     <t>489</t>
   </si>
   <si>
     <t>Médecine générale à orientation Oncogériatrie (cancérologie)</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Oncogériatrie.</t>
+  </si>
+  <si>
     <t>490</t>
   </si>
   <si>
     <t>Médecine générale à orientation Pathologies osseuses médicales</t>
   </si>
   <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Pathologies osseuses médicales.</t>
+  </si>
+  <si>
     <t>491</t>
   </si>
   <si>
@@ -3097,42 +3430,63 @@
     <t>Neuroradiologie interventionnelle</t>
   </si>
   <si>
+    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau de la sphère cérébrale.</t>
+  </si>
+  <si>
     <t>493</t>
   </si>
   <si>
     <t>Psychomotricité</t>
   </si>
   <si>
+    <t>Aide fournie, sur prescription médicale, à des personnes souffrant de différents troubles psychomoteurs - c'est-à-dire confrontées à des difficultés psychologiques exprimées par le corps - en agissant sur leurs fonctions psychomotrices : difficultés d'attention, problèmes pour se repérer dans l'espace ou dans le temps.</t>
+  </si>
+  <si>
     <t>494</t>
   </si>
   <si>
     <t>Radiologie abdominale et digestive</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère digestive.</t>
+  </si>
+  <si>
     <t>495</t>
   </si>
   <si>
     <t>Radiologie cardio-vasculaire</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau du coeur et des vaisseaux.</t>
+  </si>
+  <si>
     <t>496</t>
   </si>
   <si>
     <t>Radiologie gynécologique</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère gynécologique.</t>
+  </si>
+  <si>
     <t>497</t>
   </si>
   <si>
     <t>Radiologie interventionnelle musculosquelettique</t>
   </si>
   <si>
+    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau musculosquelettique.</t>
+  </si>
+  <si>
     <t>498</t>
   </si>
   <si>
     <t>Radiologie interventionnelle oncologique</t>
   </si>
   <si>
+    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique de pathologies oncologiques.</t>
+  </si>
+  <si>
     <t>499</t>
   </si>
   <si>
@@ -3145,78 +3499,117 @@
     <t>Radiologie interventionnelle vasculaire</t>
   </si>
   <si>
+    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau des vaisseaux sanguins.</t>
+  </si>
+  <si>
     <t>501</t>
   </si>
   <si>
     <t>Radiologie musculo-squelettique</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau musculo-squelettique.</t>
+  </si>
+  <si>
     <t>502</t>
   </si>
   <si>
     <t>Radiologie ORL et maxillo-faciale</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère ORL et maxillo-faciale.</t>
+  </si>
+  <si>
     <t>503</t>
   </si>
   <si>
     <t>Radiologie prénatale et pédiatrique</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics chez les enfants et en phase prénatale.</t>
+  </si>
+  <si>
     <t>504</t>
   </si>
   <si>
     <t>Radiologie sénologique (dont mammographie)</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau des seins.</t>
+  </si>
+  <si>
     <t>505</t>
   </si>
   <si>
     <t>Radiologie thoracique</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau thoracique.</t>
+  </si>
+  <si>
     <t>506</t>
   </si>
   <si>
     <t>Transplantation d'organe</t>
   </si>
   <si>
+    <t>Procédure thérapeutique qui vise à suppléer le fonctionnement défaillant d'un organe par un organe sain, appelé « greffon » ou « transplant » et provenant d'un donneur.</t>
+  </si>
+  <si>
     <t>507</t>
   </si>
   <si>
     <t>Uro-Radiologie</t>
   </si>
   <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère urogénitale.</t>
+  </si>
+  <si>
     <t>508</t>
   </si>
   <si>
     <t>Exploration fonctionnelle de l'exercice et du sport</t>
   </si>
   <si>
+    <t>Ensemble de tests permettant d'évaluer la capacité musculaire à l'effort à des fins de diagnostic, de suivi et de surveillance.</t>
+  </si>
+  <si>
     <t>509</t>
   </si>
   <si>
     <t>Traumatologie de l'activité physique et du sport</t>
   </si>
   <si>
+    <t>Prise en charge de l'ensemble des lésions macrotraumatiques et microtraumatiques de l'appareil locomoteur en lien avec la pratique de toute activité physique du niveau loisir au niveau compétition, qu'il s'agisse d'une lésion tendineuse, ligamentaire, osseuse ou cartilagineuse,</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
     <t>Échographie gynécologique et obstétricale (dont échographie de grossesse)</t>
   </si>
   <si>
+    <t>Echographie qui s'applique aux organes pelviens de la femme, en particulier l'utérus, les ovaires, les trompes de Fallope, ainsi que la vessie, le cul-de-sac de Douglas. L'échographie de la grossesse permettent de suivre l'évolution et le bon développement du futur bébé tout au long de ces neuf mois.</t>
+  </si>
+  <si>
     <t>511</t>
   </si>
   <si>
     <t>Accueil et hébergement spécialisé</t>
   </si>
   <si>
+    <t>Service qui vise à offrir à un enfant ou un adolescent handicapé un hébergement dans un environnement psychologique, éducatif et affectif complémentaire à celui qu'il peut trouver dans sa propre famille.</t>
+  </si>
+  <si>
     <t>512</t>
   </si>
   <si>
     <t>Accueil et orientation des victimes de violences sexuelles</t>
   </si>
   <si>
+    <t>Accueil, aide, soutien et soins aux victimes d'agressions sexuelles</t>
+  </si>
+  <si>
     <t>513</t>
   </si>
   <si>
@@ -3259,12 +3652,18 @@
     <t>Réadaptation des affections médullaires</t>
   </si>
   <si>
+    <t>Prise en charge des affections médullaires permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections médullaires sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
     <t>Réadaptation de l'obésité complexe</t>
   </si>
   <si>
+    <t>Branche des soins médicaux et de réadaptation qui vise à prévenir ou à réduire les conséquences fonctionnelles, les déficiences et les limitations d'activité liées à l'obésité complexe. L'obésité est considérée comme complexe lorsqu'elle présente l'un ou plusieurs des critères suivants : - Excès de poids majeur : indice de masse corporelle (IMC) - Evolution inquiétante de la courbe de corpulence : ascension extrême et continue - Comorbidités sévères associées au surpoids ou à l'obésité : i.e. respiratoires, articulaires, métaboliques, psychologiques ou sociales (harcèlement en milieu scolaire) ; - Antécédents d'échecs thérapeutiques ; - Situation de fragilité : difficultés psychosociales, famille non-aidante, handicap physique et/ou psychique dû à la sévérité de l'obésité, handicap physique non dû à l'obésité mais aggravé par celle-ci, pathologie psychiatrique (utilisation de psychotropes), pathologie chronique (rénale, cardiaque, osseuses, ou autres) aggravée par l'obésité, déficit cognitif, troubles du comportement, pathologie psychiatrique ; - Obésité syndromique identifiée (exemple du syndrome de Prader-Willi) ou non.</t>
+  </si>
+  <si>
     <t>521</t>
   </si>
   <si>
@@ -3277,6 +3676,9 @@
     <t>Réadaptation polyhandicap</t>
   </si>
   <si>
+    <t>Prise en charge du polyhandicap permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections liées au polyhandicap sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
     <t>523</t>
   </si>
   <si>
@@ -3307,36 +3709,54 @@
     <t>Suivi gynécologique de prévention</t>
   </si>
   <si>
+    <t>Consultation gynécologique qui permet les frottis, le dépistage, la prescription d'examens, la prescription de tous les moyens de contraception, de poser et retirer un stérilet ou un implant contraceptif, de pratiquer les IVG médicamenteuses, et de vacciner l'entourage de la femme et du nouveau-né.</t>
+  </si>
+  <si>
     <t>528</t>
   </si>
   <si>
     <t>Suivi neuropsychologique</t>
   </si>
   <si>
+    <t>Ensemble des examens, tests et épreuves psychométriques qui permettent de déterminer le retentissement cognitivo-comportemental d'une pathologie connue, de contribuer au diagnostic, ou de contribuer à une expertise médico-légale.</t>
+  </si>
+  <si>
     <t>529</t>
   </si>
   <si>
     <t>Suivi post-natal</t>
   </si>
   <si>
+    <t>Actions de prévention et de suivi éducatif en cas de besoin particulier décelé pendant la grossesse ou après l'accouchement chez les parents ou chez l'enfant réalisé par les sages-femmes.</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
     <t>Suivi prénatal (suivi de grossesse)</t>
   </si>
   <si>
+    <t>Consultations et examens complémentaires qui permettent le suivi de la grossesse normale et l'amélioration de l'identification des situations à risques de complications maternelles, obstétricales et foetales pouvant potentiellement compliquer la grossesse (hors accouchement) afin d'en adapter si besoin le suivi.</t>
+  </si>
+  <si>
     <t>531</t>
   </si>
   <si>
     <t>Réadaptation viroses chroniques</t>
   </si>
   <si>
+    <t>Prise en charge des affections chroniques secondaires à une virose permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
     <t>532</t>
   </si>
   <si>
     <t>Réadaptation lymphologie</t>
   </si>
   <si>
+    <t>Prise en charge des affections dues au lymphoedème permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
     <t>533</t>
   </si>
   <si>
@@ -3355,58 +3775,88 @@
     <t>Sexologie clinique</t>
   </si>
   <si>
+    <t>Etude de la sexualité et de la fonction érotique qui prend en charge les problématiques sexuelles psychologiques, éducationnelles, relationnelles et comportementales</t>
+  </si>
+  <si>
     <t>536</t>
   </si>
   <si>
     <t>Chirurgie oncologique thoracique</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses thoraciques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>537</t>
   </si>
   <si>
     <t>Chirurgie oncologique urologique</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses urologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>538</t>
   </si>
   <si>
     <t>Chirurgie oncologique gynécologique</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses gynécologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>539</t>
   </si>
   <si>
     <t>Chirurgie oncologique mammaire</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses mammaires. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>540</t>
   </si>
   <si>
     <t>Chirurgie oncologique neurologique</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses neurologiques (intra-crannienne et/ou intra-rachidienne). Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>541</t>
   </si>
   <si>
     <t>Chirurgie oncologique ophtalmologique</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses ophtalmologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>542</t>
   </si>
   <si>
     <t>Chirurgie oncologique dermatologique</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses dermatologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>543</t>
   </si>
   <si>
     <t>Chirurgie oncologique des os et des tissus mous</t>
   </si>
   <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses des os et des tissus mous. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
     <t>544</t>
   </si>
   <si>
     <t>Chirurgie oncologique de la thyroïde</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses de la thyroïde. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
   </si>
   <si>
     <t>545</t>
@@ -3813,17 +4263,19 @@
       <c r="C2" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -3832,22 +4284,24 @@
         <v>49</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -3856,10 +4310,10 @@
         <v>49</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -3868,10 +4322,10 @@
         <v>49</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -3880,10 +4334,10 @@
         <v>49</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -3892,10 +4346,10 @@
         <v>49</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -3904,10 +4358,10 @@
         <v>49</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -3916,10 +4370,10 @@
         <v>49</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -3928,10 +4382,10 @@
         <v>49</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -3940,10 +4394,10 @@
         <v>49</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -3952,10 +4406,10 @@
         <v>49</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" s="2"/>
     </row>
@@ -3964,10 +4418,10 @@
         <v>49</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -3976,10 +4430,10 @@
         <v>49</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -3988,10 +4442,10 @@
         <v>49</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D17" s="2"/>
     </row>
@@ -4000,10 +4454,10 @@
         <v>49</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D18" s="2"/>
     </row>
@@ -4012,10 +4466,10 @@
         <v>49</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D19" s="2"/>
     </row>
@@ -4024,10 +4478,10 @@
         <v>49</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D20" s="2"/>
     </row>
@@ -4036,10 +4490,10 @@
         <v>49</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -4048,10 +4502,10 @@
         <v>49</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D22" s="2"/>
     </row>
@@ -4060,10 +4514,10 @@
         <v>49</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D23" s="2"/>
     </row>
@@ -4072,10 +4526,10 @@
         <v>49</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D24" s="2"/>
     </row>
@@ -4084,10 +4538,10 @@
         <v>49</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D25" s="2"/>
     </row>
@@ -4096,10 +4550,10 @@
         <v>49</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D26" s="2"/>
     </row>
@@ -4108,10 +4562,10 @@
         <v>49</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D27" s="2"/>
     </row>
@@ -4120,10 +4574,10 @@
         <v>49</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D28" s="2"/>
     </row>
@@ -4132,10 +4586,10 @@
         <v>49</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -4144,10 +4598,10 @@
         <v>49</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D30" s="2"/>
     </row>
@@ -4156,10 +4610,10 @@
         <v>49</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D31" s="2"/>
     </row>
@@ -4168,10 +4622,10 @@
         <v>49</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D32" s="2"/>
     </row>
@@ -4180,34 +4634,38 @@
         <v>49</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="D33" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>116</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>119</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D35" s="2"/>
     </row>
@@ -4216,10 +4674,10 @@
         <v>49</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D36" s="2"/>
     </row>
@@ -4228,10 +4686,10 @@
         <v>49</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D37" s="2"/>
     </row>
@@ -4240,10 +4698,10 @@
         <v>49</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D38" s="2"/>
     </row>
@@ -4252,10 +4710,10 @@
         <v>49</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D39" s="2"/>
     </row>
@@ -4264,10 +4722,10 @@
         <v>49</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D40" s="2"/>
     </row>
@@ -4276,22 +4734,24 @@
         <v>49</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="D41" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>134</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D42" s="2"/>
     </row>
@@ -4300,10 +4760,10 @@
         <v>49</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D43" s="2"/>
     </row>
@@ -4312,10 +4772,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D44" s="2"/>
     </row>
@@ -4324,22 +4784,24 @@
         <v>49</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="D45" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>143</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D46" s="2"/>
     </row>
@@ -4348,10 +4810,10 @@
         <v>49</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D47" s="2"/>
     </row>
@@ -4360,10 +4822,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D48" s="2"/>
     </row>
@@ -4372,10 +4834,10 @@
         <v>49</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -4384,10 +4846,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -4396,10 +4858,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -4408,10 +4870,10 @@
         <v>49</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -4420,10 +4882,10 @@
         <v>49</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D53" s="2"/>
     </row>
@@ -4432,10 +4894,10 @@
         <v>49</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -4444,10 +4906,10 @@
         <v>49</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -4456,10 +4918,10 @@
         <v>49</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -4468,10 +4930,10 @@
         <v>49</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -4480,10 +4942,10 @@
         <v>49</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D58" s="2"/>
     </row>
@@ -4492,10 +4954,10 @@
         <v>49</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D59" s="2"/>
     </row>
@@ -4504,10 +4966,10 @@
         <v>49</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D60" s="2"/>
     </row>
@@ -4516,10 +4978,10 @@
         <v>49</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D61" s="2"/>
     </row>
@@ -4528,10 +4990,10 @@
         <v>49</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D62" s="2"/>
     </row>
@@ -4540,10 +5002,10 @@
         <v>49</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -4552,10 +5014,10 @@
         <v>49</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -4564,10 +5026,10 @@
         <v>49</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -4576,10 +5038,10 @@
         <v>49</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -4588,10 +5050,10 @@
         <v>49</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -4600,10 +5062,10 @@
         <v>49</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -4612,10 +5074,10 @@
         <v>49</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D69" s="2"/>
     </row>
@@ -4624,10 +5086,10 @@
         <v>49</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -4636,10 +5098,10 @@
         <v>49</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D71" s="2"/>
     </row>
@@ -4648,10 +5110,10 @@
         <v>49</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D72" s="2"/>
     </row>
@@ -4660,10 +5122,10 @@
         <v>49</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D73" s="2"/>
     </row>
@@ -4672,10 +5134,10 @@
         <v>49</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D74" s="2"/>
     </row>
@@ -4684,10 +5146,10 @@
         <v>49</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D75" s="2"/>
     </row>
@@ -4696,10 +5158,10 @@
         <v>49</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D76" s="2"/>
     </row>
@@ -4708,10 +5170,10 @@
         <v>49</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D77" s="2"/>
     </row>
@@ -4720,22 +5182,24 @@
         <v>49</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="D78" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>210</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D79" s="2"/>
     </row>
@@ -4744,10 +5208,10 @@
         <v>49</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D80" s="2"/>
     </row>
@@ -4756,10 +5220,10 @@
         <v>49</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -4768,10 +5232,10 @@
         <v>49</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -4780,10 +5244,10 @@
         <v>49</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -4792,10 +5256,10 @@
         <v>49</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -4804,34 +5268,38 @@
         <v>49</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="D85" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="D85" t="s" s="2">
+        <v>225</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="D86" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="D86" t="s" s="2">
+        <v>228</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -4840,10 +5308,10 @@
         <v>49</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D88" s="2"/>
     </row>
@@ -4852,10 +5320,10 @@
         <v>49</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D89" s="2"/>
     </row>
@@ -4864,10 +5332,10 @@
         <v>49</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -4876,10 +5344,10 @@
         <v>49</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -4888,10 +5356,10 @@
         <v>49</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D92" s="2"/>
     </row>
@@ -4900,10 +5368,10 @@
         <v>49</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D93" s="2"/>
     </row>
@@ -4912,10 +5380,10 @@
         <v>49</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -4924,10 +5392,10 @@
         <v>49</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D95" s="2"/>
     </row>
@@ -4936,10 +5404,10 @@
         <v>49</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -4948,10 +5416,10 @@
         <v>49</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -4960,10 +5428,10 @@
         <v>49</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="D98" s="2"/>
     </row>
@@ -4972,10 +5440,10 @@
         <v>49</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D99" s="2"/>
     </row>
@@ -4984,22 +5452,24 @@
         <v>49</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="D100" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>257</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -5008,34 +5478,38 @@
         <v>49</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="D102" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>262</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="D103" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>265</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -5044,46 +5518,52 @@
         <v>49</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="D105" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>270</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="D106" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>273</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D107" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>276</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -5092,10 +5572,10 @@
         <v>49</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -5104,10 +5584,10 @@
         <v>49</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -5116,10 +5596,10 @@
         <v>49</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -5128,10 +5608,10 @@
         <v>49</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -5140,10 +5620,10 @@
         <v>49</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -5152,10 +5632,10 @@
         <v>49</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -5164,10 +5644,10 @@
         <v>49</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -5176,10 +5656,10 @@
         <v>49</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -5188,10 +5668,10 @@
         <v>49</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -5200,22 +5680,24 @@
         <v>49</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="D118" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>299</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -5224,10 +5706,10 @@
         <v>49</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -5236,10 +5718,10 @@
         <v>49</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -5248,10 +5730,10 @@
         <v>49</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -5260,10 +5742,10 @@
         <v>49</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -5272,10 +5754,10 @@
         <v>49</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -5284,10 +5766,10 @@
         <v>49</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D125" s="2"/>
     </row>
@@ -5296,10 +5778,10 @@
         <v>49</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="D126" s="2"/>
     </row>
@@ -5308,10 +5790,10 @@
         <v>49</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="D127" s="2"/>
     </row>
@@ -5320,10 +5802,10 @@
         <v>49</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="D128" s="2"/>
     </row>
@@ -5332,10 +5814,10 @@
         <v>49</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="D129" s="2"/>
     </row>
@@ -5344,10 +5826,10 @@
         <v>49</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="D130" s="2"/>
     </row>
@@ -5356,10 +5838,10 @@
         <v>49</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="D131" s="2"/>
     </row>
@@ -5368,10 +5850,10 @@
         <v>49</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="D132" s="2"/>
     </row>
@@ -5380,22 +5862,24 @@
         <v>49</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="D133" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>330</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="D134" s="2"/>
     </row>
@@ -5404,10 +5888,10 @@
         <v>49</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="D135" s="2"/>
     </row>
@@ -5416,22 +5900,24 @@
         <v>49</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="D136" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="D136" t="s" s="2">
+        <v>337</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="D137" s="2"/>
     </row>
@@ -5440,10 +5926,10 @@
         <v>49</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D138" s="2"/>
     </row>
@@ -5452,10 +5938,10 @@
         <v>49</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="D139" s="2"/>
     </row>
@@ -5464,10 +5950,10 @@
         <v>49</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="D140" s="2"/>
     </row>
@@ -5476,10 +5962,10 @@
         <v>49</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="D141" s="2"/>
     </row>
@@ -5488,10 +5974,10 @@
         <v>49</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="D142" s="2"/>
     </row>
@@ -5500,10 +5986,10 @@
         <v>49</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -5512,10 +5998,10 @@
         <v>49</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="D144" s="2"/>
     </row>
@@ -5524,10 +6010,10 @@
         <v>49</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="D145" s="2"/>
     </row>
@@ -5536,10 +6022,10 @@
         <v>49</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="D146" s="2"/>
     </row>
@@ -5548,10 +6034,10 @@
         <v>49</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="D147" s="2"/>
     </row>
@@ -5560,10 +6046,10 @@
         <v>49</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="D148" s="2"/>
     </row>
@@ -5572,10 +6058,10 @@
         <v>49</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="D149" s="2"/>
     </row>
@@ -5584,10 +6070,10 @@
         <v>49</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="D150" s="2"/>
     </row>
@@ -5596,10 +6082,10 @@
         <v>49</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="D151" s="2"/>
     </row>
@@ -5608,10 +6094,10 @@
         <v>49</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="D152" s="2"/>
     </row>
@@ -5620,10 +6106,10 @@
         <v>49</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -5632,10 +6118,10 @@
         <v>49</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="D154" s="2"/>
     </row>
@@ -5644,10 +6130,10 @@
         <v>49</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="D155" s="2"/>
     </row>
@@ -5656,10 +6142,10 @@
         <v>49</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="D156" s="2"/>
     </row>
@@ -5668,10 +6154,10 @@
         <v>49</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -5680,10 +6166,10 @@
         <v>49</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D158" s="2"/>
     </row>
@@ -5692,10 +6178,10 @@
         <v>49</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="D159" s="2"/>
     </row>
@@ -5704,10 +6190,10 @@
         <v>49</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="D160" s="2"/>
     </row>
@@ -5716,10 +6202,10 @@
         <v>49</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="D161" s="2"/>
     </row>
@@ -5728,10 +6214,10 @@
         <v>49</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -5740,10 +6226,10 @@
         <v>49</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -5752,10 +6238,10 @@
         <v>49</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -5764,22 +6250,24 @@
         <v>49</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="D165" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="D165" t="s" s="2">
+        <v>396</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -5788,10 +6276,10 @@
         <v>49</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -5800,10 +6288,10 @@
         <v>49</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -5812,22 +6300,24 @@
         <v>49</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="D169" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="D169" t="s" s="2">
+        <v>405</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -5836,22 +6326,24 @@
         <v>49</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="D171" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="D171" t="s" s="2">
+        <v>410</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -5860,22 +6352,24 @@
         <v>49</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="D173" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="D173" t="s" s="2">
+        <v>415</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -5884,10 +6378,10 @@
         <v>49</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -5896,10 +6390,10 @@
         <v>49</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -5908,10 +6402,10 @@
         <v>49</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -5920,10 +6414,10 @@
         <v>49</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -5932,34 +6426,38 @@
         <v>49</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="D179" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="D179" t="s" s="2">
+        <v>427</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="D180" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="D180" t="s" s="2">
+        <v>430</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -5968,10 +6466,10 @@
         <v>49</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -5980,10 +6478,10 @@
         <v>49</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -5992,10 +6490,10 @@
         <v>49</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -6004,10 +6502,10 @@
         <v>49</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -6016,10 +6514,10 @@
         <v>49</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -6028,106 +6526,122 @@
         <v>49</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="D187" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="D187" t="s" s="2">
+        <v>445</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="D188" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="D188" t="s" s="2">
+        <v>448</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="D189" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="D189" t="s" s="2">
+        <v>451</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="D190" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="D190" t="s" s="2">
+        <v>454</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="D191" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="D191" t="s" s="2">
+        <v>457</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="D192" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="D192" t="s" s="2">
+        <v>460</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="D193" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="D193" t="s" s="2">
+        <v>463</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="D194" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="D194" t="s" s="2">
+        <v>466</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -6136,34 +6650,38 @@
         <v>49</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="D196" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="D196" t="s" s="2">
+        <v>471</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="D197" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="D197" t="s" s="2">
+        <v>474</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -6172,58 +6690,66 @@
         <v>49</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="D199" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="D199" t="s" s="2">
+        <v>479</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="D200" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="D200" t="s" s="2">
+        <v>482</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>447</v>
+        <v>483</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="D201" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>485</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="D202" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="D202" t="s" s="2">
+        <v>488</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -6232,10 +6758,10 @@
         <v>49</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>453</v>
+        <v>491</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="D204" s="2"/>
     </row>
@@ -6244,10 +6770,10 @@
         <v>49</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>455</v>
+        <v>493</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>456</v>
+        <v>494</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -6256,10 +6782,10 @@
         <v>49</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>457</v>
+        <v>495</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>458</v>
+        <v>496</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -6268,10 +6794,10 @@
         <v>49</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -6280,10 +6806,10 @@
         <v>49</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -6292,10 +6818,10 @@
         <v>49</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -6304,10 +6830,10 @@
         <v>49</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>466</v>
+        <v>504</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -6316,10 +6842,10 @@
         <v>49</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>468</v>
+        <v>506</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -6328,10 +6854,10 @@
         <v>49</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>469</v>
+        <v>507</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -6340,10 +6866,10 @@
         <v>49</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -6352,10 +6878,10 @@
         <v>49</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>473</v>
+        <v>511</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -6364,10 +6890,10 @@
         <v>49</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>475</v>
+        <v>513</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>476</v>
+        <v>514</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -6376,10 +6902,10 @@
         <v>49</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>477</v>
+        <v>515</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -6388,10 +6914,10 @@
         <v>49</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>479</v>
+        <v>517</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -6400,10 +6926,10 @@
         <v>49</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>481</v>
+        <v>519</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>482</v>
+        <v>520</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -6412,10 +6938,10 @@
         <v>49</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>483</v>
+        <v>521</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>484</v>
+        <v>522</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -6424,10 +6950,10 @@
         <v>49</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>485</v>
+        <v>523</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -6436,10 +6962,10 @@
         <v>49</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>487</v>
+        <v>525</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>488</v>
+        <v>526</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -6448,10 +6974,10 @@
         <v>49</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -6460,10 +6986,10 @@
         <v>49</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>491</v>
+        <v>529</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -6472,10 +6998,10 @@
         <v>49</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>493</v>
+        <v>531</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>494</v>
+        <v>532</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6484,10 +7010,10 @@
         <v>49</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>495</v>
+        <v>533</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>496</v>
+        <v>534</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -6496,10 +7022,10 @@
         <v>49</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>497</v>
+        <v>535</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>498</v>
+        <v>536</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -6508,22 +7034,24 @@
         <v>49</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="D227" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="D227" t="s" s="2">
+        <v>539</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -6532,10 +7060,10 @@
         <v>49</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -6544,10 +7072,10 @@
         <v>49</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>506</v>
+        <v>545</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -6556,10 +7084,10 @@
         <v>49</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -6568,22 +7096,24 @@
         <v>49</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="D232" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="D232" t="s" s="2">
+        <v>550</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>511</v>
+        <v>551</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>512</v>
+        <v>552</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -6592,70 +7122,80 @@
         <v>49</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>513</v>
+        <v>553</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="D234" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="D234" t="s" s="2">
+        <v>555</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="D235" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="D235" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>517</v>
+        <v>559</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="D236" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="D236" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>519</v>
+        <v>561</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="D237" s="2"/>
+        <v>562</v>
+      </c>
+      <c r="D237" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>521</v>
+        <v>563</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="D238" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="D238" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>523</v>
+        <v>565</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>524</v>
+        <v>566</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -6664,22 +7204,24 @@
         <v>49</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>525</v>
+        <v>567</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="D240" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="D240" t="s" s="2">
+        <v>569</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>527</v>
+        <v>570</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>528</v>
+        <v>571</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -6688,22 +7230,24 @@
         <v>49</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>529</v>
+        <v>572</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="D242" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="D242" t="s" s="2">
+        <v>574</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>532</v>
+        <v>576</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -6712,22 +7256,24 @@
         <v>49</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>533</v>
+        <v>577</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="D244" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="D244" t="s" s="2">
+        <v>579</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>535</v>
+        <v>580</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>536</v>
+        <v>581</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -6736,22 +7282,24 @@
         <v>49</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>537</v>
+        <v>582</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="D246" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="D246" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -6760,10 +7308,10 @@
         <v>49</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>541</v>
+        <v>586</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>542</v>
+        <v>587</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -6772,10 +7320,10 @@
         <v>49</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>544</v>
+        <v>589</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -6784,10 +7332,10 @@
         <v>49</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>545</v>
+        <v>590</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>546</v>
+        <v>591</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -6796,10 +7344,10 @@
         <v>49</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>547</v>
+        <v>592</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>548</v>
+        <v>593</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -6808,10 +7356,10 @@
         <v>49</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>549</v>
+        <v>594</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>550</v>
+        <v>595</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -6820,10 +7368,10 @@
         <v>49</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>551</v>
+        <v>596</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>552</v>
+        <v>597</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -6832,10 +7380,10 @@
         <v>49</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>554</v>
+        <v>599</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -6844,10 +7392,10 @@
         <v>49</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>555</v>
+        <v>600</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>556</v>
+        <v>601</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -6856,10 +7404,10 @@
         <v>49</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>557</v>
+        <v>602</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>558</v>
+        <v>603</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -6868,10 +7416,10 @@
         <v>49</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>559</v>
+        <v>604</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>560</v>
+        <v>605</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -6880,10 +7428,10 @@
         <v>49</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>561</v>
+        <v>606</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -6892,10 +7440,10 @@
         <v>49</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>563</v>
+        <v>608</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>564</v>
+        <v>609</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -6904,10 +7452,10 @@
         <v>49</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>565</v>
+        <v>610</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>566</v>
+        <v>611</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -6916,10 +7464,10 @@
         <v>49</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>567</v>
+        <v>612</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>568</v>
+        <v>613</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -6928,10 +7476,10 @@
         <v>49</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>569</v>
+        <v>614</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -6940,10 +7488,10 @@
         <v>49</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>571</v>
+        <v>616</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>572</v>
+        <v>617</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -6952,10 +7500,10 @@
         <v>49</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>573</v>
+        <v>618</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -6964,10 +7512,10 @@
         <v>49</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>575</v>
+        <v>620</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>576</v>
+        <v>621</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -6976,10 +7524,10 @@
         <v>49</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>577</v>
+        <v>622</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>578</v>
+        <v>623</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -6988,10 +7536,10 @@
         <v>49</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>579</v>
+        <v>624</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>580</v>
+        <v>625</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -7000,10 +7548,10 @@
         <v>49</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>581</v>
+        <v>626</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -7012,10 +7560,10 @@
         <v>49</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>584</v>
+        <v>629</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -7024,10 +7572,10 @@
         <v>49</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>585</v>
+        <v>630</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>586</v>
+        <v>631</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -7036,10 +7584,10 @@
         <v>49</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>587</v>
+        <v>632</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>588</v>
+        <v>633</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -7048,10 +7596,10 @@
         <v>49</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="D272" s="2"/>
     </row>
@@ -7060,10 +7608,10 @@
         <v>49</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>591</v>
+        <v>636</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>592</v>
+        <v>637</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -7072,10 +7620,10 @@
         <v>49</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>593</v>
+        <v>638</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>594</v>
+        <v>639</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -7084,10 +7632,10 @@
         <v>49</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>595</v>
+        <v>640</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>596</v>
+        <v>641</v>
       </c>
       <c r="D275" s="2"/>
     </row>
@@ -7096,10 +7644,10 @@
         <v>49</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>597</v>
+        <v>642</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>598</v>
+        <v>643</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -7108,10 +7656,10 @@
         <v>49</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>599</v>
+        <v>644</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -7120,10 +7668,10 @@
         <v>49</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>601</v>
+        <v>646</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -7132,10 +7680,10 @@
         <v>49</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>603</v>
+        <v>648</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>604</v>
+        <v>649</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -7144,22 +7692,24 @@
         <v>49</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>605</v>
+        <v>650</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="D280" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="D280" t="s" s="2">
+        <v>652</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>607</v>
+        <v>653</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>608</v>
+        <v>654</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -7168,34 +7718,38 @@
         <v>49</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>609</v>
+        <v>655</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="D282" s="2"/>
+        <v>656</v>
+      </c>
+      <c r="D282" t="s" s="2">
+        <v>657</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>611</v>
+        <v>658</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="D283" s="2"/>
+        <v>659</v>
+      </c>
+      <c r="D283" t="s" s="2">
+        <v>660</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>613</v>
+        <v>661</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -7204,10 +7758,10 @@
         <v>49</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>616</v>
+        <v>664</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -7216,10 +7770,10 @@
         <v>49</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>617</v>
+        <v>665</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>618</v>
+        <v>666</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -7228,10 +7782,10 @@
         <v>49</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>619</v>
+        <v>667</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -7240,22 +7794,24 @@
         <v>49</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="D288" s="2"/>
+        <v>669</v>
+      </c>
+      <c r="D288" t="s" s="2">
+        <v>670</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>622</v>
+        <v>671</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>623</v>
+        <v>672</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -7264,10 +7820,10 @@
         <v>49</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>624</v>
+        <v>673</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>625</v>
+        <v>674</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -7276,46 +7832,52 @@
         <v>49</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>626</v>
+        <v>675</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="D291" s="2"/>
+        <v>676</v>
+      </c>
+      <c r="D291" t="s" s="2">
+        <v>677</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>628</v>
+        <v>678</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="D292" s="2"/>
+        <v>679</v>
+      </c>
+      <c r="D292" t="s" s="2">
+        <v>680</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>630</v>
+        <v>681</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="D293" s="2"/>
+        <v>682</v>
+      </c>
+      <c r="D293" t="s" s="2">
+        <v>683</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>632</v>
+        <v>684</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>633</v>
+        <v>685</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -7324,10 +7886,10 @@
         <v>49</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>634</v>
+        <v>686</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>635</v>
+        <v>687</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -7336,10 +7898,10 @@
         <v>49</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>636</v>
+        <v>688</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>637</v>
+        <v>689</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -7348,10 +7910,10 @@
         <v>49</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>638</v>
+        <v>690</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>639</v>
+        <v>691</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -7360,10 +7922,10 @@
         <v>49</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>640</v>
+        <v>692</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>641</v>
+        <v>693</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -7372,10 +7934,10 @@
         <v>49</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>642</v>
+        <v>694</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>643</v>
+        <v>695</v>
       </c>
       <c r="D299" s="2"/>
     </row>
@@ -7384,10 +7946,10 @@
         <v>49</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>644</v>
+        <v>696</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>645</v>
+        <v>697</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -7396,10 +7958,10 @@
         <v>49</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>646</v>
+        <v>698</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>647</v>
+        <v>699</v>
       </c>
       <c r="D301" s="2"/>
     </row>
@@ -7408,10 +7970,10 @@
         <v>49</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>648</v>
+        <v>700</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>649</v>
+        <v>701</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -7420,22 +7982,24 @@
         <v>49</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>650</v>
+        <v>702</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="D303" s="2"/>
+        <v>703</v>
+      </c>
+      <c r="D303" t="s" s="2">
+        <v>704</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>652</v>
+        <v>705</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>653</v>
+        <v>706</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -7444,10 +8008,10 @@
         <v>49</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>654</v>
+        <v>707</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>655</v>
+        <v>708</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -7456,10 +8020,10 @@
         <v>49</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>656</v>
+        <v>709</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>657</v>
+        <v>710</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -7468,10 +8032,10 @@
         <v>49</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>658</v>
+        <v>711</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>659</v>
+        <v>712</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -7480,10 +8044,10 @@
         <v>49</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>660</v>
+        <v>713</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>661</v>
+        <v>714</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -7492,10 +8056,10 @@
         <v>49</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>662</v>
+        <v>715</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>663</v>
+        <v>716</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -7504,10 +8068,10 @@
         <v>49</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>664</v>
+        <v>717</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>665</v>
+        <v>718</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7516,10 +8080,10 @@
         <v>49</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>666</v>
+        <v>719</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>667</v>
+        <v>720</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7528,10 +8092,10 @@
         <v>49</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>668</v>
+        <v>721</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>669</v>
+        <v>722</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7540,34 +8104,38 @@
         <v>49</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>670</v>
+        <v>723</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="D313" s="2"/>
+        <v>724</v>
+      </c>
+      <c r="D313" t="s" s="2">
+        <v>725</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>672</v>
+        <v>726</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="D314" s="2"/>
+        <v>727</v>
+      </c>
+      <c r="D314" t="s" s="2">
+        <v>728</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>674</v>
+        <v>729</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>675</v>
+        <v>730</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7576,10 +8144,10 @@
         <v>49</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>676</v>
+        <v>731</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>677</v>
+        <v>732</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7588,10 +8156,10 @@
         <v>49</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>678</v>
+        <v>733</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>679</v>
+        <v>734</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7600,10 +8168,10 @@
         <v>49</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>680</v>
+        <v>735</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>681</v>
+        <v>736</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7612,10 +8180,10 @@
         <v>49</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>682</v>
+        <v>737</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>683</v>
+        <v>738</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7624,10 +8192,10 @@
         <v>49</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>684</v>
+        <v>739</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>685</v>
+        <v>740</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7636,10 +8204,10 @@
         <v>49</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>686</v>
+        <v>741</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>687</v>
+        <v>742</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7648,10 +8216,10 @@
         <v>49</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>688</v>
+        <v>743</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>689</v>
+        <v>744</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7660,10 +8228,10 @@
         <v>49</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>690</v>
+        <v>745</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>691</v>
+        <v>746</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7672,10 +8240,10 @@
         <v>49</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>692</v>
+        <v>747</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>693</v>
+        <v>748</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7684,10 +8252,10 @@
         <v>49</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>694</v>
+        <v>749</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>695</v>
+        <v>750</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7696,22 +8264,24 @@
         <v>49</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>696</v>
+        <v>751</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="D326" s="2"/>
+        <v>752</v>
+      </c>
+      <c r="D326" t="s" s="2">
+        <v>753</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>698</v>
+        <v>754</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>699</v>
+        <v>755</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7720,10 +8290,10 @@
         <v>49</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>701</v>
+        <v>757</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7732,10 +8302,10 @@
         <v>49</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>702</v>
+        <v>758</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>703</v>
+        <v>759</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7744,10 +8314,10 @@
         <v>49</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>704</v>
+        <v>760</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>705</v>
+        <v>761</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7756,10 +8326,10 @@
         <v>49</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>706</v>
+        <v>762</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>707</v>
+        <v>763</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7768,10 +8338,10 @@
         <v>49</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>708</v>
+        <v>764</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>709</v>
+        <v>765</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7780,10 +8350,10 @@
         <v>49</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>710</v>
+        <v>766</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>711</v>
+        <v>767</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7792,10 +8362,10 @@
         <v>49</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>712</v>
+        <v>768</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7804,34 +8374,38 @@
         <v>49</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>714</v>
+        <v>770</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="D335" s="2"/>
+        <v>771</v>
+      </c>
+      <c r="D335" t="s" s="2">
+        <v>772</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>716</v>
+        <v>773</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="D336" s="2"/>
+        <v>774</v>
+      </c>
+      <c r="D336" t="s" s="2">
+        <v>775</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>718</v>
+        <v>776</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>719</v>
+        <v>777</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7840,10 +8414,10 @@
         <v>49</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>720</v>
+        <v>778</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>721</v>
+        <v>779</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7852,46 +8426,52 @@
         <v>49</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>722</v>
+        <v>780</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="D339" s="2"/>
+        <v>781</v>
+      </c>
+      <c r="D339" t="s" s="2">
+        <v>782</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>724</v>
+        <v>783</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="D340" s="2"/>
+        <v>784</v>
+      </c>
+      <c r="D340" t="s" s="2">
+        <v>785</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>726</v>
+        <v>786</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="D341" s="2"/>
+        <v>787</v>
+      </c>
+      <c r="D341" t="s" s="2">
+        <v>788</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>728</v>
+        <v>789</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>729</v>
+        <v>790</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7900,10 +8480,10 @@
         <v>49</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>730</v>
+        <v>791</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>731</v>
+        <v>792</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7912,10 +8492,10 @@
         <v>49</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>732</v>
+        <v>793</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>733</v>
+        <v>794</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7924,10 +8504,10 @@
         <v>49</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>734</v>
+        <v>795</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>735</v>
+        <v>796</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7936,10 +8516,10 @@
         <v>49</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>736</v>
+        <v>797</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>737</v>
+        <v>798</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7948,10 +8528,10 @@
         <v>49</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>738</v>
+        <v>799</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>739</v>
+        <v>800</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7960,22 +8540,24 @@
         <v>49</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>740</v>
+        <v>801</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="D348" s="2"/>
+        <v>802</v>
+      </c>
+      <c r="D348" t="s" s="2">
+        <v>803</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>742</v>
+        <v>804</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>743</v>
+        <v>805</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7984,22 +8566,24 @@
         <v>49</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>744</v>
+        <v>806</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="D350" s="2"/>
+        <v>807</v>
+      </c>
+      <c r="D350" t="s" s="2">
+        <v>803</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>746</v>
+        <v>808</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>747</v>
+        <v>809</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -8008,10 +8592,10 @@
         <v>49</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>748</v>
+        <v>810</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>749</v>
+        <v>811</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -8020,10 +8604,10 @@
         <v>49</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>750</v>
+        <v>812</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>751</v>
+        <v>813</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -8032,10 +8616,10 @@
         <v>49</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>752</v>
+        <v>814</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>753</v>
+        <v>815</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -8044,10 +8628,10 @@
         <v>49</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>754</v>
+        <v>816</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>755</v>
+        <v>817</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -8056,10 +8640,10 @@
         <v>49</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>756</v>
+        <v>818</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>757</v>
+        <v>819</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -8068,10 +8652,10 @@
         <v>49</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>758</v>
+        <v>820</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>759</v>
+        <v>821</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -8080,10 +8664,10 @@
         <v>49</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>760</v>
+        <v>822</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>761</v>
+        <v>823</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -8092,10 +8676,10 @@
         <v>49</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>762</v>
+        <v>824</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>763</v>
+        <v>825</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -8104,10 +8688,10 @@
         <v>49</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>764</v>
+        <v>826</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>765</v>
+        <v>827</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -8116,10 +8700,10 @@
         <v>49</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>766</v>
+        <v>828</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>767</v>
+        <v>829</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -8128,10 +8712,10 @@
         <v>49</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>768</v>
+        <v>830</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>769</v>
+        <v>831</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -8140,10 +8724,10 @@
         <v>49</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>770</v>
+        <v>832</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>771</v>
+        <v>833</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -8152,10 +8736,10 @@
         <v>49</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>772</v>
+        <v>834</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>773</v>
+        <v>835</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -8164,10 +8748,10 @@
         <v>49</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>774</v>
+        <v>836</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>775</v>
+        <v>837</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -8176,10 +8760,10 @@
         <v>49</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>776</v>
+        <v>838</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>777</v>
+        <v>839</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -8188,10 +8772,10 @@
         <v>49</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>778</v>
+        <v>840</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>779</v>
+        <v>841</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -8200,22 +8784,24 @@
         <v>49</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>780</v>
+        <v>842</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="D368" s="2"/>
+        <v>843</v>
+      </c>
+      <c r="D368" t="s" s="2">
+        <v>844</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>782</v>
+        <v>845</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>783</v>
+        <v>846</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -8224,10 +8810,10 @@
         <v>49</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>784</v>
+        <v>847</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>785</v>
+        <v>848</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -8236,10 +8822,10 @@
         <v>49</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>786</v>
+        <v>849</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>787</v>
+        <v>850</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -8248,10 +8834,10 @@
         <v>49</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>788</v>
+        <v>851</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>789</v>
+        <v>852</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -8260,10 +8846,10 @@
         <v>49</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>790</v>
+        <v>853</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>791</v>
+        <v>854</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -8272,10 +8858,10 @@
         <v>49</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>792</v>
+        <v>855</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>793</v>
+        <v>856</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -8284,10 +8870,10 @@
         <v>49</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>794</v>
+        <v>857</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>795</v>
+        <v>858</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -8296,10 +8882,10 @@
         <v>49</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>796</v>
+        <v>859</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>797</v>
+        <v>860</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -8308,10 +8894,10 @@
         <v>49</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>798</v>
+        <v>861</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>799</v>
+        <v>862</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -8320,10 +8906,10 @@
         <v>49</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>800</v>
+        <v>863</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>801</v>
+        <v>864</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -8332,10 +8918,10 @@
         <v>49</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>802</v>
+        <v>865</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>803</v>
+        <v>866</v>
       </c>
       <c r="D379" s="2"/>
     </row>
@@ -8344,10 +8930,10 @@
         <v>49</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>805</v>
+        <v>868</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -8356,10 +8942,10 @@
         <v>49</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>806</v>
+        <v>869</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>807</v>
+        <v>870</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -8368,10 +8954,10 @@
         <v>49</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>808</v>
+        <v>871</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>809</v>
+        <v>872</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -8380,10 +8966,10 @@
         <v>49</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>810</v>
+        <v>873</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>811</v>
+        <v>874</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -8392,10 +8978,10 @@
         <v>49</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>812</v>
+        <v>875</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>813</v>
+        <v>876</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -8404,10 +8990,10 @@
         <v>49</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>814</v>
+        <v>877</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>815</v>
+        <v>878</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -8416,10 +9002,10 @@
         <v>49</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>816</v>
+        <v>879</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>817</v>
+        <v>880</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -8428,10 +9014,10 @@
         <v>49</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>818</v>
+        <v>881</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>819</v>
+        <v>882</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -8440,10 +9026,10 @@
         <v>49</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>820</v>
+        <v>883</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>821</v>
+        <v>884</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -8452,10 +9038,10 @@
         <v>49</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>822</v>
+        <v>885</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>823</v>
+        <v>886</v>
       </c>
       <c r="D389" s="2"/>
     </row>
@@ -8464,10 +9050,10 @@
         <v>49</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>824</v>
+        <v>887</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>825</v>
+        <v>888</v>
       </c>
       <c r="D390" s="2"/>
     </row>
@@ -8476,10 +9062,10 @@
         <v>49</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>826</v>
+        <v>889</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>827</v>
+        <v>890</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8488,10 +9074,10 @@
         <v>49</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>828</v>
+        <v>891</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>829</v>
+        <v>892</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8500,10 +9086,10 @@
         <v>49</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>830</v>
+        <v>893</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>831</v>
+        <v>894</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8512,10 +9098,10 @@
         <v>49</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>832</v>
+        <v>895</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>833</v>
+        <v>896</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8524,10 +9110,10 @@
         <v>49</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>834</v>
+        <v>897</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>835</v>
+        <v>898</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8536,10 +9122,10 @@
         <v>49</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>836</v>
+        <v>899</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>837</v>
+        <v>900</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8548,10 +9134,10 @@
         <v>49</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>838</v>
+        <v>901</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>839</v>
+        <v>902</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8560,22 +9146,24 @@
         <v>49</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>840</v>
+        <v>903</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="D398" s="2"/>
+        <v>904</v>
+      </c>
+      <c r="D398" t="s" s="2">
+        <v>905</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>842</v>
+        <v>906</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>843</v>
+        <v>907</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8584,10 +9172,10 @@
         <v>49</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>844</v>
+        <v>908</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>845</v>
+        <v>909</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8596,10 +9184,10 @@
         <v>49</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>846</v>
+        <v>910</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>847</v>
+        <v>911</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8608,10 +9196,10 @@
         <v>49</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>848</v>
+        <v>912</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>849</v>
+        <v>913</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8620,10 +9208,10 @@
         <v>49</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>850</v>
+        <v>914</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>851</v>
+        <v>915</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8632,10 +9220,10 @@
         <v>49</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>852</v>
+        <v>916</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>853</v>
+        <v>917</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8644,22 +9232,24 @@
         <v>49</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>854</v>
+        <v>918</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="D405" s="2"/>
+        <v>919</v>
+      </c>
+      <c r="D405" t="s" s="2">
+        <v>920</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>856</v>
+        <v>921</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>857</v>
+        <v>922</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8668,10 +9258,10 @@
         <v>49</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>858</v>
+        <v>923</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>859</v>
+        <v>924</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8680,10 +9270,10 @@
         <v>49</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>860</v>
+        <v>925</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>861</v>
+        <v>926</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8692,10 +9282,10 @@
         <v>49</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>862</v>
+        <v>927</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>863</v>
+        <v>928</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8704,34 +9294,38 @@
         <v>49</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>864</v>
+        <v>929</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="D410" s="2"/>
+        <v>930</v>
+      </c>
+      <c r="D410" t="s" s="2">
+        <v>931</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>866</v>
+        <v>932</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="D411" s="2"/>
+        <v>933</v>
+      </c>
+      <c r="D411" t="s" s="2">
+        <v>934</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>868</v>
+        <v>935</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>869</v>
+        <v>936</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8740,10 +9334,10 @@
         <v>49</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>870</v>
+        <v>937</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>871</v>
+        <v>938</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8752,10 +9346,10 @@
         <v>49</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>872</v>
+        <v>939</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>873</v>
+        <v>940</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8764,10 +9358,10 @@
         <v>49</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>874</v>
+        <v>941</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>875</v>
+        <v>942</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8776,10 +9370,10 @@
         <v>49</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>876</v>
+        <v>943</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>877</v>
+        <v>944</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8788,10 +9382,10 @@
         <v>49</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>878</v>
+        <v>945</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>879</v>
+        <v>946</v>
       </c>
       <c r="D417" s="2"/>
     </row>
@@ -8800,10 +9394,10 @@
         <v>49</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>880</v>
+        <v>947</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>881</v>
+        <v>948</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -8812,10 +9406,10 @@
         <v>49</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>882</v>
+        <v>949</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>883</v>
+        <v>950</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8824,10 +9418,10 @@
         <v>49</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>884</v>
+        <v>951</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>885</v>
+        <v>952</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8836,10 +9430,10 @@
         <v>49</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>886</v>
+        <v>953</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>887</v>
+        <v>954</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8848,10 +9442,10 @@
         <v>49</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>888</v>
+        <v>955</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>889</v>
+        <v>956</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8860,10 +9454,10 @@
         <v>49</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>890</v>
+        <v>957</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>891</v>
+        <v>958</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8872,10 +9466,10 @@
         <v>49</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>892</v>
+        <v>959</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>893</v>
+        <v>960</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -8884,10 +9478,10 @@
         <v>49</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>894</v>
+        <v>961</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>895</v>
+        <v>962</v>
       </c>
       <c r="D425" s="2"/>
     </row>
@@ -8896,10 +9490,10 @@
         <v>49</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>896</v>
+        <v>963</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>897</v>
+        <v>964</v>
       </c>
       <c r="D426" s="2"/>
     </row>
@@ -8908,10 +9502,10 @@
         <v>49</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>898</v>
+        <v>965</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>899</v>
+        <v>966</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -8920,10 +9514,10 @@
         <v>49</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>900</v>
+        <v>967</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>901</v>
+        <v>968</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -8932,10 +9526,10 @@
         <v>49</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>902</v>
+        <v>969</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>903</v>
+        <v>970</v>
       </c>
       <c r="D429" s="2"/>
     </row>
@@ -8944,10 +9538,10 @@
         <v>49</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>904</v>
+        <v>971</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>905</v>
+        <v>972</v>
       </c>
       <c r="D430" s="2"/>
     </row>
@@ -8956,10 +9550,10 @@
         <v>49</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>906</v>
+        <v>973</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>907</v>
+        <v>974</v>
       </c>
       <c r="D431" s="2"/>
     </row>
@@ -8968,10 +9562,10 @@
         <v>49</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>908</v>
+        <v>975</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>909</v>
+        <v>976</v>
       </c>
       <c r="D432" s="2"/>
     </row>
@@ -8980,10 +9574,10 @@
         <v>49</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>910</v>
+        <v>977</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>911</v>
+        <v>978</v>
       </c>
       <c r="D433" s="2"/>
     </row>
@@ -8992,10 +9586,10 @@
         <v>49</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>912</v>
+        <v>979</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>913</v>
+        <v>980</v>
       </c>
       <c r="D434" s="2"/>
     </row>
@@ -9004,34 +9598,38 @@
         <v>49</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>914</v>
+        <v>981</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="D435" s="2"/>
+        <v>982</v>
+      </c>
+      <c r="D435" t="s" s="2">
+        <v>983</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>916</v>
+        <v>984</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>917</v>
-      </c>
-      <c r="D436" s="2"/>
+        <v>985</v>
+      </c>
+      <c r="D436" t="s" s="2">
+        <v>986</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>918</v>
+        <v>987</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>919</v>
+        <v>988</v>
       </c>
       <c r="D437" s="2"/>
     </row>
@@ -9040,22 +9638,24 @@
         <v>49</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>920</v>
+        <v>989</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="D438" s="2"/>
+        <v>990</v>
+      </c>
+      <c r="D438" t="s" s="2">
+        <v>991</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>922</v>
+        <v>992</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>923</v>
+        <v>993</v>
       </c>
       <c r="D439" s="2"/>
     </row>
@@ -9064,178 +9664,206 @@
         <v>49</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>924</v>
+        <v>994</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="D440" s="2"/>
+        <v>995</v>
+      </c>
+      <c r="D440" t="s" s="2">
+        <v>996</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>926</v>
+        <v>997</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="D441" s="2"/>
+        <v>998</v>
+      </c>
+      <c r="D441" t="s" s="2">
+        <v>999</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>928</v>
+        <v>1000</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>929</v>
-      </c>
-      <c r="D442" s="2"/>
+        <v>1001</v>
+      </c>
+      <c r="D442" t="s" s="2">
+        <v>1002</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>930</v>
+        <v>1003</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>931</v>
-      </c>
-      <c r="D443" s="2"/>
+        <v>1004</v>
+      </c>
+      <c r="D443" t="s" s="2">
+        <v>1005</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>932</v>
+        <v>1006</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>933</v>
-      </c>
-      <c r="D444" s="2"/>
+        <v>1007</v>
+      </c>
+      <c r="D444" t="s" s="2">
+        <v>1008</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>934</v>
+        <v>1009</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="D445" s="2"/>
+        <v>1010</v>
+      </c>
+      <c r="D445" t="s" s="2">
+        <v>1011</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>936</v>
+        <v>1012</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>937</v>
-      </c>
-      <c r="D446" s="2"/>
+        <v>1013</v>
+      </c>
+      <c r="D446" t="s" s="2">
+        <v>1014</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>938</v>
+        <v>1015</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>939</v>
-      </c>
-      <c r="D447" s="2"/>
+        <v>1016</v>
+      </c>
+      <c r="D447" t="s" s="2">
+        <v>1017</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>940</v>
+        <v>1018</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>941</v>
-      </c>
-      <c r="D448" s="2"/>
+        <v>1019</v>
+      </c>
+      <c r="D448" t="s" s="2">
+        <v>1020</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>942</v>
+        <v>1021</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>943</v>
-      </c>
-      <c r="D449" s="2"/>
+        <v>1022</v>
+      </c>
+      <c r="D449" t="s" s="2">
+        <v>1023</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>944</v>
+        <v>1024</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>945</v>
-      </c>
-      <c r="D450" s="2"/>
+        <v>1025</v>
+      </c>
+      <c r="D450" t="s" s="2">
+        <v>1026</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>946</v>
+        <v>1027</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>947</v>
-      </c>
-      <c r="D451" s="2"/>
+        <v>1028</v>
+      </c>
+      <c r="D451" t="s" s="2">
+        <v>1029</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>948</v>
+        <v>1030</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>949</v>
-      </c>
-      <c r="D452" s="2"/>
+        <v>1031</v>
+      </c>
+      <c r="D452" t="s" s="2">
+        <v>1032</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>950</v>
+        <v>1033</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>951</v>
-      </c>
-      <c r="D453" s="2"/>
+        <v>1034</v>
+      </c>
+      <c r="D453" t="s" s="2">
+        <v>1035</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>952</v>
+        <v>1036</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>953</v>
+        <v>1037</v>
       </c>
       <c r="D454" s="2"/>
     </row>
@@ -9244,46 +9872,52 @@
         <v>49</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>954</v>
+        <v>1038</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="D455" s="2"/>
+        <v>1039</v>
+      </c>
+      <c r="D455" t="s" s="2">
+        <v>1040</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>956</v>
+        <v>1041</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>957</v>
-      </c>
-      <c r="D456" s="2"/>
+        <v>1042</v>
+      </c>
+      <c r="D456" t="s" s="2">
+        <v>1043</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>958</v>
+        <v>1044</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="D457" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="D457" t="s" s="2">
+        <v>1045</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>959</v>
+        <v>1046</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>960</v>
+        <v>1047</v>
       </c>
       <c r="D458" s="2"/>
     </row>
@@ -9292,406 +9926,472 @@
         <v>49</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>961</v>
+        <v>1048</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="D459" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="D459" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>962</v>
+        <v>1049</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="D460" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="D460" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>963</v>
+        <v>1050</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>964</v>
-      </c>
-      <c r="D461" s="2"/>
+        <v>1051</v>
+      </c>
+      <c r="D461" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>965</v>
+        <v>1052</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="D462" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="D462" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>966</v>
+        <v>1053</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="D463" s="2"/>
+        <v>562</v>
+      </c>
+      <c r="D463" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>967</v>
+        <v>1054</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>968</v>
-      </c>
-      <c r="D464" s="2"/>
+        <v>1055</v>
+      </c>
+      <c r="D464" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>969</v>
+        <v>1056</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>970</v>
-      </c>
-      <c r="D465" s="2"/>
+        <v>1057</v>
+      </c>
+      <c r="D465" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>971</v>
+        <v>1058</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>972</v>
-      </c>
-      <c r="D466" s="2"/>
+        <v>1059</v>
+      </c>
+      <c r="D466" t="s" s="2">
+        <v>558</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>973</v>
+        <v>1060</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>974</v>
-      </c>
-      <c r="D467" s="2"/>
+        <v>1061</v>
+      </c>
+      <c r="D467" t="s" s="2">
+        <v>1062</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>975</v>
+        <v>1063</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>976</v>
-      </c>
-      <c r="D468" s="2"/>
+        <v>1064</v>
+      </c>
+      <c r="D468" t="s" s="2">
+        <v>1065</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>977</v>
+        <v>1066</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>978</v>
-      </c>
-      <c r="D469" s="2"/>
+        <v>1067</v>
+      </c>
+      <c r="D469" t="s" s="2">
+        <v>1068</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>979</v>
+        <v>1069</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>980</v>
-      </c>
-      <c r="D470" s="2"/>
+        <v>1070</v>
+      </c>
+      <c r="D470" t="s" s="2">
+        <v>1071</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>982</v>
-      </c>
-      <c r="D471" s="2"/>
+        <v>1073</v>
+      </c>
+      <c r="D471" t="s" s="2">
+        <v>1074</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>983</v>
+        <v>1075</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>984</v>
-      </c>
-      <c r="D472" s="2"/>
+        <v>1076</v>
+      </c>
+      <c r="D472" t="s" s="2">
+        <v>1077</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>985</v>
+        <v>1078</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>986</v>
-      </c>
-      <c r="D473" s="2"/>
+        <v>1079</v>
+      </c>
+      <c r="D473" t="s" s="2">
+        <v>1080</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>987</v>
+        <v>1081</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>988</v>
-      </c>
-      <c r="D474" s="2"/>
+        <v>1082</v>
+      </c>
+      <c r="D474" t="s" s="2">
+        <v>1083</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>989</v>
+        <v>1084</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>990</v>
-      </c>
-      <c r="D475" s="2"/>
+        <v>1085</v>
+      </c>
+      <c r="D475" t="s" s="2">
+        <v>1086</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>991</v>
+        <v>1087</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>992</v>
-      </c>
-      <c r="D476" s="2"/>
+        <v>1088</v>
+      </c>
+      <c r="D476" t="s" s="2">
+        <v>1089</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>993</v>
+        <v>1090</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>994</v>
-      </c>
-      <c r="D477" s="2"/>
+        <v>1091</v>
+      </c>
+      <c r="D477" t="s" s="2">
+        <v>1092</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>995</v>
+        <v>1093</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>996</v>
-      </c>
-      <c r="D478" s="2"/>
+        <v>1094</v>
+      </c>
+      <c r="D478" t="s" s="2">
+        <v>1095</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>997</v>
+        <v>1096</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>998</v>
-      </c>
-      <c r="D479" s="2"/>
+        <v>1097</v>
+      </c>
+      <c r="D479" t="s" s="2">
+        <v>1098</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>999</v>
+        <v>1099</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D480" s="2"/>
+        <v>1100</v>
+      </c>
+      <c r="D480" t="s" s="2">
+        <v>803</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D481" s="2"/>
+        <v>1102</v>
+      </c>
+      <c r="D481" t="s" s="2">
+        <v>1103</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1003</v>
+        <v>1104</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D482" s="2"/>
+        <v>1105</v>
+      </c>
+      <c r="D482" t="s" s="2">
+        <v>1106</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1005</v>
+        <v>1107</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1006</v>
-      </c>
-      <c r="D483" s="2"/>
+        <v>1108</v>
+      </c>
+      <c r="D483" t="s" s="2">
+        <v>1109</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1007</v>
+        <v>1110</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1008</v>
-      </c>
-      <c r="D484" s="2"/>
+        <v>1111</v>
+      </c>
+      <c r="D484" t="s" s="2">
+        <v>1112</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1009</v>
+        <v>1113</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1010</v>
-      </c>
-      <c r="D485" s="2"/>
+        <v>1114</v>
+      </c>
+      <c r="D485" t="s" s="2">
+        <v>1115</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1011</v>
+        <v>1116</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1012</v>
-      </c>
-      <c r="D486" s="2"/>
+        <v>1117</v>
+      </c>
+      <c r="D486" t="s" s="2">
+        <v>1118</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1013</v>
+        <v>1119</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1014</v>
-      </c>
-      <c r="D487" s="2"/>
+        <v>1120</v>
+      </c>
+      <c r="D487" t="s" s="2">
+        <v>1121</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1015</v>
+        <v>1122</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1016</v>
-      </c>
-      <c r="D488" s="2"/>
+        <v>1123</v>
+      </c>
+      <c r="D488" t="s" s="2">
+        <v>1124</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1017</v>
+        <v>1125</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1018</v>
-      </c>
-      <c r="D489" s="2"/>
+        <v>1126</v>
+      </c>
+      <c r="D489" t="s" s="2">
+        <v>1127</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1019</v>
+        <v>1128</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1020</v>
-      </c>
-      <c r="D490" s="2"/>
+        <v>1129</v>
+      </c>
+      <c r="D490" t="s" s="2">
+        <v>1130</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1021</v>
+        <v>1131</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1022</v>
-      </c>
-      <c r="D491" s="2"/>
+        <v>1132</v>
+      </c>
+      <c r="D491" t="s" s="2">
+        <v>1133</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1023</v>
+        <v>1134</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1024</v>
+        <v>1135</v>
       </c>
       <c r="D492" s="2"/>
     </row>
@@ -9700,94 +10400,108 @@
         <v>49</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1025</v>
+        <v>1136</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1026</v>
-      </c>
-      <c r="D493" s="2"/>
+        <v>1137</v>
+      </c>
+      <c r="D493" t="s" s="2">
+        <v>1138</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1027</v>
+        <v>1139</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1028</v>
-      </c>
-      <c r="D494" s="2"/>
+        <v>1140</v>
+      </c>
+      <c r="D494" t="s" s="2">
+        <v>1141</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1029</v>
+        <v>1142</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1030</v>
-      </c>
-      <c r="D495" s="2"/>
+        <v>1143</v>
+      </c>
+      <c r="D495" t="s" s="2">
+        <v>1144</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1031</v>
+        <v>1145</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1032</v>
-      </c>
-      <c r="D496" s="2"/>
+        <v>1146</v>
+      </c>
+      <c r="D496" t="s" s="2">
+        <v>1147</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1033</v>
+        <v>1148</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1034</v>
-      </c>
-      <c r="D497" s="2"/>
+        <v>1149</v>
+      </c>
+      <c r="D497" t="s" s="2">
+        <v>1150</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1035</v>
+        <v>1151</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1036</v>
-      </c>
-      <c r="D498" s="2"/>
+        <v>1152</v>
+      </c>
+      <c r="D498" t="s" s="2">
+        <v>1153</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1037</v>
+        <v>1154</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1038</v>
-      </c>
-      <c r="D499" s="2"/>
+        <v>1155</v>
+      </c>
+      <c r="D499" t="s" s="2">
+        <v>1156</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1039</v>
+        <v>1157</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1040</v>
+        <v>1158</v>
       </c>
       <c r="D500" s="2"/>
     </row>
@@ -9796,166 +10510,192 @@
         <v>49</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1041</v>
+        <v>1159</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1042</v>
-      </c>
-      <c r="D501" s="2"/>
+        <v>1160</v>
+      </c>
+      <c r="D501" t="s" s="2">
+        <v>1161</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1043</v>
+        <v>1162</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1044</v>
-      </c>
-      <c r="D502" s="2"/>
+        <v>1163</v>
+      </c>
+      <c r="D502" t="s" s="2">
+        <v>1164</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1045</v>
+        <v>1165</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1046</v>
-      </c>
-      <c r="D503" s="2"/>
+        <v>1166</v>
+      </c>
+      <c r="D503" t="s" s="2">
+        <v>1167</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1047</v>
+        <v>1168</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1048</v>
-      </c>
-      <c r="D504" s="2"/>
+        <v>1169</v>
+      </c>
+      <c r="D504" t="s" s="2">
+        <v>1170</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1049</v>
+        <v>1171</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1050</v>
-      </c>
-      <c r="D505" s="2"/>
+        <v>1172</v>
+      </c>
+      <c r="D505" t="s" s="2">
+        <v>1173</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1051</v>
+        <v>1174</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1052</v>
-      </c>
-      <c r="D506" s="2"/>
+        <v>1175</v>
+      </c>
+      <c r="D506" t="s" s="2">
+        <v>1176</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1053</v>
+        <v>1177</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1054</v>
-      </c>
-      <c r="D507" s="2"/>
+        <v>1178</v>
+      </c>
+      <c r="D507" t="s" s="2">
+        <v>1179</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1055</v>
+        <v>1180</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1056</v>
-      </c>
-      <c r="D508" s="2"/>
+        <v>1181</v>
+      </c>
+      <c r="D508" t="s" s="2">
+        <v>1182</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1057</v>
+        <v>1183</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1058</v>
-      </c>
-      <c r="D509" s="2"/>
+        <v>1184</v>
+      </c>
+      <c r="D509" t="s" s="2">
+        <v>1185</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1059</v>
+        <v>1186</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1060</v>
-      </c>
-      <c r="D510" s="2"/>
+        <v>1187</v>
+      </c>
+      <c r="D510" t="s" s="2">
+        <v>1188</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1061</v>
+        <v>1189</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1062</v>
-      </c>
-      <c r="D511" s="2"/>
+        <v>1190</v>
+      </c>
+      <c r="D511" t="s" s="2">
+        <v>1191</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1063</v>
+        <v>1192</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1064</v>
-      </c>
-      <c r="D512" s="2"/>
+        <v>1193</v>
+      </c>
+      <c r="D512" t="s" s="2">
+        <v>1194</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1065</v>
+        <v>1195</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1066</v>
-      </c>
-      <c r="D513" s="2"/>
+        <v>1196</v>
+      </c>
+      <c r="D513" t="s" s="2">
+        <v>1197</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1067</v>
+        <v>1198</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1068</v>
+        <v>1199</v>
       </c>
       <c r="D514" s="2"/>
     </row>
@@ -9964,10 +10704,10 @@
         <v>49</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1069</v>
+        <v>1200</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1070</v>
+        <v>1201</v>
       </c>
       <c r="D515" s="2"/>
     </row>
@@ -9976,10 +10716,10 @@
         <v>49</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1071</v>
+        <v>1202</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1072</v>
+        <v>1203</v>
       </c>
       <c r="D516" s="2"/>
     </row>
@@ -9988,10 +10728,10 @@
         <v>49</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1073</v>
+        <v>1204</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1074</v>
+        <v>1205</v>
       </c>
       <c r="D517" s="2"/>
     </row>
@@ -10000,10 +10740,10 @@
         <v>49</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1075</v>
+        <v>1206</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1076</v>
+        <v>1207</v>
       </c>
       <c r="D518" s="2"/>
     </row>
@@ -10012,10 +10752,10 @@
         <v>49</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1077</v>
+        <v>1208</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1078</v>
+        <v>1209</v>
       </c>
       <c r="D519" s="2"/>
     </row>
@@ -10024,34 +10764,38 @@
         <v>49</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1079</v>
+        <v>1210</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1080</v>
-      </c>
-      <c r="D520" s="2"/>
+        <v>1211</v>
+      </c>
+      <c r="D520" t="s" s="2">
+        <v>1212</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1081</v>
+        <v>1213</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1082</v>
-      </c>
-      <c r="D521" s="2"/>
+        <v>1214</v>
+      </c>
+      <c r="D521" t="s" s="2">
+        <v>1215</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1083</v>
+        <v>1216</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1084</v>
+        <v>1217</v>
       </c>
       <c r="D522" s="2"/>
     </row>
@@ -10060,22 +10804,24 @@
         <v>49</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1085</v>
+        <v>1218</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1086</v>
-      </c>
-      <c r="D523" s="2"/>
+        <v>1219</v>
+      </c>
+      <c r="D523" t="s" s="2">
+        <v>1220</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1087</v>
+        <v>1221</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1088</v>
+        <v>1222</v>
       </c>
       <c r="D524" s="2"/>
     </row>
@@ -10084,10 +10830,10 @@
         <v>49</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1089</v>
+        <v>1223</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1090</v>
+        <v>1224</v>
       </c>
       <c r="D525" s="2"/>
     </row>
@@ -10096,10 +10842,10 @@
         <v>49</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1091</v>
+        <v>1225</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1092</v>
+        <v>1226</v>
       </c>
       <c r="D526" s="2"/>
     </row>
@@ -10108,10 +10854,10 @@
         <v>49</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1093</v>
+        <v>1227</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1094</v>
+        <v>1228</v>
       </c>
       <c r="D527" s="2"/>
     </row>
@@ -10120,82 +10866,94 @@
         <v>49</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1095</v>
+        <v>1229</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1096</v>
-      </c>
-      <c r="D528" s="2"/>
+        <v>1230</v>
+      </c>
+      <c r="D528" t="s" s="2">
+        <v>1231</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1097</v>
+        <v>1232</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1098</v>
-      </c>
-      <c r="D529" s="2"/>
+        <v>1233</v>
+      </c>
+      <c r="D529" t="s" s="2">
+        <v>1234</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1099</v>
+        <v>1235</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="D530" s="2"/>
+        <v>1236</v>
+      </c>
+      <c r="D530" t="s" s="2">
+        <v>1237</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1101</v>
+        <v>1238</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1102</v>
-      </c>
-      <c r="D531" s="2"/>
+        <v>1239</v>
+      </c>
+      <c r="D531" t="s" s="2">
+        <v>1240</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1103</v>
+        <v>1241</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1104</v>
-      </c>
-      <c r="D532" s="2"/>
+        <v>1242</v>
+      </c>
+      <c r="D532" t="s" s="2">
+        <v>1243</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1105</v>
+        <v>1244</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1106</v>
-      </c>
-      <c r="D533" s="2"/>
+        <v>1245</v>
+      </c>
+      <c r="D533" t="s" s="2">
+        <v>1246</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1107</v>
+        <v>1247</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1108</v>
+        <v>1248</v>
       </c>
       <c r="D534" s="2"/>
     </row>
@@ -10204,10 +10962,10 @@
         <v>49</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1109</v>
+        <v>1249</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1110</v>
+        <v>1250</v>
       </c>
       <c r="D535" s="2"/>
     </row>
@@ -10216,130 +10974,150 @@
         <v>49</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1111</v>
+        <v>1251</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1112</v>
-      </c>
-      <c r="D536" s="2"/>
+        <v>1252</v>
+      </c>
+      <c r="D536" t="s" s="2">
+        <v>1253</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1113</v>
+        <v>1254</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1114</v>
-      </c>
-      <c r="D537" s="2"/>
+        <v>1255</v>
+      </c>
+      <c r="D537" t="s" s="2">
+        <v>1256</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1115</v>
+        <v>1257</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1116</v>
-      </c>
-      <c r="D538" s="2"/>
+        <v>1258</v>
+      </c>
+      <c r="D538" t="s" s="2">
+        <v>1259</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1117</v>
+        <v>1260</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1118</v>
-      </c>
-      <c r="D539" s="2"/>
+        <v>1261</v>
+      </c>
+      <c r="D539" t="s" s="2">
+        <v>1262</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1119</v>
+        <v>1263</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1120</v>
-      </c>
-      <c r="D540" s="2"/>
+        <v>1264</v>
+      </c>
+      <c r="D540" t="s" s="2">
+        <v>1265</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1121</v>
+        <v>1266</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1122</v>
-      </c>
-      <c r="D541" s="2"/>
+        <v>1267</v>
+      </c>
+      <c r="D541" t="s" s="2">
+        <v>1268</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1123</v>
+        <v>1269</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1124</v>
-      </c>
-      <c r="D542" s="2"/>
+        <v>1270</v>
+      </c>
+      <c r="D542" t="s" s="2">
+        <v>1271</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1125</v>
+        <v>1272</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1126</v>
-      </c>
-      <c r="D543" s="2"/>
+        <v>1273</v>
+      </c>
+      <c r="D543" t="s" s="2">
+        <v>1274</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1127</v>
+        <v>1275</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1128</v>
-      </c>
-      <c r="D544" s="2"/>
+        <v>1276</v>
+      </c>
+      <c r="D544" t="s" s="2">
+        <v>1277</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1129</v>
+        <v>1278</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1130</v>
-      </c>
-      <c r="D545" s="2"/>
+        <v>1279</v>
+      </c>
+      <c r="D545" t="s" s="2">
+        <v>1280</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1131</v>
+        <v>1281</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1132</v>
+        <v>1282</v>
       </c>
       <c r="D546" s="2"/>
     </row>
